--- a/data/H131_20260619_12.xlsx
+++ b/data/H131_20260619_12.xlsx
@@ -598,7 +598,7 @@
         <v>1074.0</v>
       </c>
       <c r="J4" s="2">
-        <v>606.0</v>
+        <v>622.0</v>
       </c>
       <c r="K4" s="2">
         <v>1.0</v>
@@ -610,13 +610,13 @@
         <v>0.0</v>
       </c>
       <c r="N4" s="2">
-        <v>606.0</v>
+        <v>622.0</v>
       </c>
       <c r="O4" s="2">
-        <v>275.0</v>
+        <v>287.0</v>
       </c>
       <c r="P4" s="2">
-        <v>331.0</v>
+        <v>335.0</v>
       </c>
       <c r="Q4" s="2">
         <v>0.0</v>
@@ -811,7 +811,7 @@
         <v>515.0</v>
       </c>
       <c r="J7" s="2">
-        <v>377.0</v>
+        <v>388.0</v>
       </c>
       <c r="K7" s="2">
         <v>1.0</v>
@@ -823,13 +823,13 @@
         <v>0.0</v>
       </c>
       <c r="N7" s="2">
-        <v>377.0</v>
+        <v>388.0</v>
       </c>
       <c r="O7" s="2">
-        <v>196.0</v>
+        <v>206.0</v>
       </c>
       <c r="P7" s="2">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="Q7" s="2">
         <v>0.0</v>
@@ -882,7 +882,7 @@
         <v>711.0</v>
       </c>
       <c r="J8" s="2">
-        <v>503.0</v>
+        <v>504.0</v>
       </c>
       <c r="K8" s="2">
         <v>1.0</v>
@@ -894,10 +894,10 @@
         <v>0.0</v>
       </c>
       <c r="N8" s="2">
-        <v>503.0</v>
+        <v>504.0</v>
       </c>
       <c r="O8" s="2">
-        <v>292.0</v>
+        <v>293.0</v>
       </c>
       <c r="P8" s="2">
         <v>211.0</v>
@@ -1166,7 +1166,7 @@
         <v>815.0</v>
       </c>
       <c r="J12" s="2">
-        <v>752.0</v>
+        <v>754.0</v>
       </c>
       <c r="K12" s="2">
         <v>1.0</v>
@@ -1178,13 +1178,13 @@
         <v>0.0</v>
       </c>
       <c r="N12" s="2">
-        <v>752.0</v>
+        <v>754.0</v>
       </c>
       <c r="O12" s="2">
         <v>433.0</v>
       </c>
       <c r="P12" s="2">
-        <v>319.0</v>
+        <v>321.0</v>
       </c>
       <c r="Q12" s="2">
         <v>0.0</v>
@@ -1308,7 +1308,7 @@
         <v>1342.0</v>
       </c>
       <c r="J14" s="2">
-        <v>863.0</v>
+        <v>928.0</v>
       </c>
       <c r="K14" s="2">
         <v>1.0</v>
@@ -1320,13 +1320,13 @@
         <v>0.0</v>
       </c>
       <c r="N14" s="2">
-        <v>863.0</v>
+        <v>928.0</v>
       </c>
       <c r="O14" s="2">
-        <v>459.0</v>
+        <v>502.0</v>
       </c>
       <c r="P14" s="2">
-        <v>402.0</v>
+        <v>424.0</v>
       </c>
       <c r="Q14" s="2">
         <v>2.0</v>
@@ -1379,7 +1379,7 @@
         <v>791.0</v>
       </c>
       <c r="J15" s="2">
-        <v>603.0</v>
+        <v>613.0</v>
       </c>
       <c r="K15" s="2">
         <v>1.0</v>
@@ -1391,13 +1391,13 @@
         <v>0.0</v>
       </c>
       <c r="N15" s="2">
-        <v>603.0</v>
+        <v>613.0</v>
       </c>
       <c r="O15" s="2">
-        <v>299.0</v>
+        <v>307.0</v>
       </c>
       <c r="P15" s="2">
-        <v>304.0</v>
+        <v>306.0</v>
       </c>
       <c r="Q15" s="2">
         <v>0.0</v>
@@ -1521,7 +1521,7 @@
         <v>829.0</v>
       </c>
       <c r="J17" s="2">
-        <v>653.0</v>
+        <v>675.0</v>
       </c>
       <c r="K17" s="2">
         <v>1.0</v>
@@ -1533,13 +1533,13 @@
         <v>0.0</v>
       </c>
       <c r="N17" s="2">
-        <v>653.0</v>
+        <v>675.0</v>
       </c>
       <c r="O17" s="2">
-        <v>346.0</v>
+        <v>362.0</v>
       </c>
       <c r="P17" s="2">
-        <v>307.0</v>
+        <v>313.0</v>
       </c>
       <c r="Q17" s="2">
         <v>0.0</v>
@@ -1663,7 +1663,7 @@
         <v>940.0</v>
       </c>
       <c r="J19" s="2">
-        <v>697.0</v>
+        <v>751.0</v>
       </c>
       <c r="K19" s="2">
         <v>1.0</v>
@@ -1675,13 +1675,13 @@
         <v>0.0</v>
       </c>
       <c r="N19" s="2">
-        <v>697.0</v>
+        <v>751.0</v>
       </c>
       <c r="O19" s="2">
-        <v>368.0</v>
+        <v>398.0</v>
       </c>
       <c r="P19" s="2">
-        <v>329.0</v>
+        <v>353.0</v>
       </c>
       <c r="Q19" s="2">
         <v>0.0</v>
@@ -1693,7 +1693,7 @@
         <v>19.0</v>
       </c>
       <c r="T19" s="2">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="U19" s="2">
         <v>1.0</v>
@@ -1702,7 +1702,7 @@
         <v>0.0</v>
       </c>
       <c r="W19" s="2">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="20">
@@ -1734,7 +1734,7 @@
         <v>1257.0</v>
       </c>
       <c r="J20" s="2">
-        <v>1042.0</v>
+        <v>1048.0</v>
       </c>
       <c r="K20" s="2">
         <v>1.0</v>
@@ -1746,19 +1746,19 @@
         <v>1.0</v>
       </c>
       <c r="N20" s="2">
-        <v>1041.0</v>
+        <v>1047.0</v>
       </c>
       <c r="O20" s="2">
-        <v>599.0</v>
+        <v>602.0</v>
       </c>
       <c r="P20" s="2">
-        <v>443.0</v>
+        <v>446.0</v>
       </c>
       <c r="Q20" s="2">
         <v>0.0</v>
       </c>
       <c r="R20" s="2">
-        <v>17.0</v>
+        <v>20.0</v>
       </c>
       <c r="S20" s="2">
         <v>22.0</v>
@@ -1773,7 +1773,7 @@
         <v>0.0</v>
       </c>
       <c r="W20" s="2">
-        <v>44.0</v>
+        <v>47.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -1832,10 +1832,10 @@
         <v>35.0</v>
       </c>
       <c r="S21" s="2">
-        <v>12.0</v>
+        <v>30.0</v>
       </c>
       <c r="T21" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="U21" s="2">
         <v>0.0</v>
@@ -1844,7 +1844,7 @@
         <v>0.0</v>
       </c>
       <c r="W21" s="2">
-        <v>47.0</v>
+        <v>69.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -1876,7 +1876,7 @@
         <v>1003.0</v>
       </c>
       <c r="J22" s="2">
-        <v>848.0</v>
+        <v>851.0</v>
       </c>
       <c r="K22" s="2">
         <v>1.0</v>
@@ -1888,10 +1888,10 @@
         <v>0.0</v>
       </c>
       <c r="N22" s="2">
-        <v>848.0</v>
+        <v>851.0</v>
       </c>
       <c r="O22" s="2">
-        <v>472.0</v>
+        <v>475.0</v>
       </c>
       <c r="P22" s="2">
         <v>376.0</v>
@@ -1947,7 +1947,7 @@
         <v>762.0</v>
       </c>
       <c r="J23" s="2">
-        <v>361.0</v>
+        <v>387.0</v>
       </c>
       <c r="K23" s="2">
         <v>1.0</v>
@@ -1959,13 +1959,13 @@
         <v>0.0</v>
       </c>
       <c r="N23" s="2">
-        <v>361.0</v>
+        <v>387.0</v>
       </c>
       <c r="O23" s="2">
-        <v>175.0</v>
+        <v>188.0</v>
       </c>
       <c r="P23" s="2">
-        <v>186.0</v>
+        <v>199.0</v>
       </c>
       <c r="Q23" s="2">
         <v>0.0</v>
@@ -2018,7 +2018,7 @@
         <v>1296.0</v>
       </c>
       <c r="J24" s="2">
-        <v>759.0</v>
+        <v>763.0</v>
       </c>
       <c r="K24" s="2">
         <v>1.0</v>
@@ -2030,22 +2030,22 @@
         <v>0.0</v>
       </c>
       <c r="N24" s="2">
-        <v>759.0</v>
+        <v>763.0</v>
       </c>
       <c r="O24" s="2">
-        <v>438.0</v>
+        <v>440.0</v>
       </c>
       <c r="P24" s="2">
-        <v>305.0</v>
+        <v>307.0</v>
       </c>
       <c r="Q24" s="2">
         <v>16.0</v>
       </c>
       <c r="R24" s="2">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="S24" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="T24" s="2">
         <v>1.0</v>
@@ -2057,7 +2057,7 @@
         <v>0.0</v>
       </c>
       <c r="W24" s="2">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -2089,7 +2089,7 @@
         <v>372.0</v>
       </c>
       <c r="J25" s="2">
-        <v>354.0</v>
+        <v>359.0</v>
       </c>
       <c r="K25" s="2">
         <v>1.0</v>
@@ -2101,10 +2101,10 @@
         <v>0.0</v>
       </c>
       <c r="N25" s="2">
-        <v>354.0</v>
+        <v>359.0</v>
       </c>
       <c r="O25" s="2">
-        <v>251.0</v>
+        <v>256.0</v>
       </c>
       <c r="P25" s="2">
         <v>103.0</v>
@@ -2122,13 +2122,13 @@
         <v>0.0</v>
       </c>
       <c r="U25" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="V25" s="2">
         <v>0.0</v>
       </c>
       <c r="W25" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -2302,7 +2302,7 @@
         <v>1349.0</v>
       </c>
       <c r="J28" s="2">
-        <v>1014.0</v>
+        <v>1015.0</v>
       </c>
       <c r="K28" s="2">
         <v>1.0</v>
@@ -2314,10 +2314,10 @@
         <v>0.0</v>
       </c>
       <c r="N28" s="2">
-        <v>1014.0</v>
+        <v>1015.0</v>
       </c>
       <c r="O28" s="2">
-        <v>555.0</v>
+        <v>556.0</v>
       </c>
       <c r="P28" s="2">
         <v>457.0</v>
@@ -2373,7 +2373,7 @@
         <v>1280.0</v>
       </c>
       <c r="J29" s="2">
-        <v>422.0</v>
+        <v>494.0</v>
       </c>
       <c r="K29" s="2">
         <v>1.0</v>
@@ -2385,13 +2385,13 @@
         <v>0.0</v>
       </c>
       <c r="N29" s="2">
-        <v>422.0</v>
+        <v>494.0</v>
       </c>
       <c r="O29" s="2">
-        <v>74.0</v>
+        <v>108.0</v>
       </c>
       <c r="P29" s="2">
-        <v>216.0</v>
+        <v>254.0</v>
       </c>
       <c r="Q29" s="2">
         <v>132.0</v>
@@ -2515,7 +2515,7 @@
         <v>1214.0</v>
       </c>
       <c r="J31" s="2">
-        <v>814.0</v>
+        <v>859.0</v>
       </c>
       <c r="K31" s="2">
         <v>1.0</v>
@@ -2527,16 +2527,16 @@
         <v>0.0</v>
       </c>
       <c r="N31" s="2">
-        <v>814.0</v>
+        <v>859.0</v>
       </c>
       <c r="O31" s="2">
-        <v>433.0</v>
+        <v>465.0</v>
       </c>
       <c r="P31" s="2">
-        <v>376.0</v>
+        <v>387.0</v>
       </c>
       <c r="Q31" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="R31" s="2">
         <v>1.0</v>
@@ -2657,7 +2657,7 @@
         <v>346.0</v>
       </c>
       <c r="J33" s="2">
-        <v>309.0</v>
+        <v>312.0</v>
       </c>
       <c r="K33" s="2">
         <v>1.0</v>
@@ -2669,16 +2669,16 @@
         <v>0.0</v>
       </c>
       <c r="N33" s="2">
-        <v>309.0</v>
+        <v>312.0</v>
       </c>
       <c r="O33" s="2">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="P33" s="2">
-        <v>171.0</v>
+        <v>172.0</v>
       </c>
       <c r="Q33" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R33" s="2">
         <v>9.0</v>
@@ -2799,7 +2799,7 @@
         <v>554.0</v>
       </c>
       <c r="J35" s="2">
-        <v>449.0</v>
+        <v>472.0</v>
       </c>
       <c r="K35" s="2">
         <v>1.0</v>
@@ -2811,13 +2811,13 @@
         <v>0.0</v>
       </c>
       <c r="N35" s="2">
-        <v>449.0</v>
+        <v>472.0</v>
       </c>
       <c r="O35" s="2">
-        <v>237.0</v>
+        <v>253.0</v>
       </c>
       <c r="P35" s="2">
-        <v>203.0</v>
+        <v>210.0</v>
       </c>
       <c r="Q35" s="2">
         <v>9.0</v>
@@ -2870,7 +2870,7 @@
         <v>1103.0</v>
       </c>
       <c r="J36" s="2">
-        <v>604.0</v>
+        <v>626.0</v>
       </c>
       <c r="K36" s="2">
         <v>1.0</v>
@@ -2882,13 +2882,13 @@
         <v>0.0</v>
       </c>
       <c r="N36" s="2">
-        <v>604.0</v>
+        <v>626.0</v>
       </c>
       <c r="O36" s="2">
-        <v>278.0</v>
+        <v>293.0</v>
       </c>
       <c r="P36" s="2">
-        <v>323.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q36" s="2">
         <v>3.0</v>
@@ -2897,19 +2897,19 @@
         <v>45.0</v>
       </c>
       <c r="S36" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="T36" s="2">
         <v>0.0</v>
       </c>
       <c r="U36" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="V36" s="2">
         <v>0.0</v>
       </c>
       <c r="W36" s="2">
-        <v>71.0</v>
+        <v>73.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -2941,7 +2941,7 @@
         <v>586.0</v>
       </c>
       <c r="J37" s="2">
-        <v>462.0</v>
+        <v>463.0</v>
       </c>
       <c r="K37" s="2">
         <v>1.0</v>
@@ -2953,13 +2953,13 @@
         <v>0.0</v>
       </c>
       <c r="N37" s="2">
-        <v>462.0</v>
+        <v>463.0</v>
       </c>
       <c r="O37" s="2">
         <v>241.0</v>
       </c>
       <c r="P37" s="2">
-        <v>217.0</v>
+        <v>218.0</v>
       </c>
       <c r="Q37" s="2">
         <v>4.0</v>
@@ -3083,7 +3083,7 @@
         <v>588.0</v>
       </c>
       <c r="J39" s="2">
-        <v>434.0</v>
+        <v>447.0</v>
       </c>
       <c r="K39" s="2">
         <v>1.0</v>
@@ -3095,13 +3095,13 @@
         <v>0.0</v>
       </c>
       <c r="N39" s="2">
-        <v>434.0</v>
+        <v>447.0</v>
       </c>
       <c r="O39" s="2">
-        <v>218.0</v>
+        <v>224.0</v>
       </c>
       <c r="P39" s="2">
-        <v>216.0</v>
+        <v>223.0</v>
       </c>
       <c r="Q39" s="2">
         <v>0.0</v>
@@ -3154,7 +3154,7 @@
         <v>1249.0</v>
       </c>
       <c r="J40" s="2">
-        <v>1147.0</v>
+        <v>1186.0</v>
       </c>
       <c r="K40" s="2">
         <v>1.0</v>
@@ -3166,13 +3166,13 @@
         <v>0.0</v>
       </c>
       <c r="N40" s="2">
-        <v>1147.0</v>
+        <v>1186.0</v>
       </c>
       <c r="O40" s="2">
-        <v>650.0</v>
+        <v>683.0</v>
       </c>
       <c r="P40" s="2">
-        <v>490.0</v>
+        <v>496.0</v>
       </c>
       <c r="Q40" s="2">
         <v>7.0</v>
@@ -3225,7 +3225,7 @@
         <v>1244.0</v>
       </c>
       <c r="J41" s="2">
-        <v>918.0</v>
+        <v>923.0</v>
       </c>
       <c r="K41" s="2">
         <v>1.0</v>
@@ -3237,10 +3237,10 @@
         <v>0.0</v>
       </c>
       <c r="N41" s="2">
-        <v>918.0</v>
+        <v>923.0</v>
       </c>
       <c r="O41" s="2">
-        <v>432.0</v>
+        <v>437.0</v>
       </c>
       <c r="P41" s="2">
         <v>486.0</v>
@@ -3296,7 +3296,7 @@
         <v>1005.0</v>
       </c>
       <c r="J42" s="2">
-        <v>565.0</v>
+        <v>611.0</v>
       </c>
       <c r="K42" s="2">
         <v>1.0</v>
@@ -3308,22 +3308,22 @@
         <v>0.0</v>
       </c>
       <c r="N42" s="2">
-        <v>565.0</v>
+        <v>611.0</v>
       </c>
       <c r="O42" s="2">
-        <v>370.0</v>
+        <v>405.0</v>
       </c>
       <c r="P42" s="2">
-        <v>195.0</v>
+        <v>206.0</v>
       </c>
       <c r="Q42" s="2">
         <v>0.0</v>
       </c>
       <c r="R42" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="S42" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="T42" s="2">
         <v>0.0</v>
@@ -3335,7 +3335,7 @@
         <v>0.0</v>
       </c>
       <c r="W42" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -3391,7 +3391,7 @@
         <v>1.0</v>
       </c>
       <c r="R43" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="S43" s="2">
         <v>0.0</v>
@@ -3406,7 +3406,7 @@
         <v>0.0</v>
       </c>
       <c r="W43" s="2">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -3438,7 +3438,7 @@
         <v>1094.0</v>
       </c>
       <c r="J44" s="2">
-        <v>1044.0</v>
+        <v>1053.0</v>
       </c>
       <c r="K44" s="2">
         <v>1.0</v>
@@ -3450,16 +3450,16 @@
         <v>0.0</v>
       </c>
       <c r="N44" s="2">
-        <v>1044.0</v>
+        <v>1053.0</v>
       </c>
       <c r="O44" s="2">
-        <v>563.0</v>
+        <v>566.0</v>
       </c>
       <c r="P44" s="2">
-        <v>480.0</v>
+        <v>484.0</v>
       </c>
       <c r="Q44" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="R44" s="2">
         <v>20.0</v>
@@ -3468,7 +3468,7 @@
         <v>13.0</v>
       </c>
       <c r="T44" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="U44" s="2">
         <v>5.0</v>
@@ -3477,7 +3477,7 @@
         <v>0.0</v>
       </c>
       <c r="W44" s="2">
-        <v>39.0</v>
+        <v>41.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
@@ -3509,7 +3509,7 @@
         <v>1213.0</v>
       </c>
       <c r="J45" s="2">
-        <v>1043.0</v>
+        <v>1059.0</v>
       </c>
       <c r="K45" s="2">
         <v>1.0</v>
@@ -3521,16 +3521,16 @@
         <v>1.0</v>
       </c>
       <c r="N45" s="2">
-        <v>1042.0</v>
+        <v>1058.0</v>
       </c>
       <c r="O45" s="2">
-        <v>488.0</v>
+        <v>497.0</v>
       </c>
       <c r="P45" s="2">
-        <v>524.0</v>
+        <v>529.0</v>
       </c>
       <c r="Q45" s="2">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="R45" s="2">
         <v>48.0</v>
@@ -3793,7 +3793,7 @@
         <v>1437.0</v>
       </c>
       <c r="J49" s="2">
-        <v>1019.0</v>
+        <v>1028.0</v>
       </c>
       <c r="K49" s="2">
         <v>1.0</v>
@@ -3805,13 +3805,13 @@
         <v>0.0</v>
       </c>
       <c r="N49" s="2">
-        <v>1019.0</v>
+        <v>1028.0</v>
       </c>
       <c r="O49" s="2">
-        <v>534.0</v>
+        <v>541.0</v>
       </c>
       <c r="P49" s="2">
-        <v>453.0</v>
+        <v>455.0</v>
       </c>
       <c r="Q49" s="2">
         <v>32.0</v>
@@ -3935,7 +3935,7 @@
         <v>878.0</v>
       </c>
       <c r="J51" s="2">
-        <v>779.0</v>
+        <v>782.0</v>
       </c>
       <c r="K51" s="2">
         <v>1.0</v>
@@ -3947,13 +3947,13 @@
         <v>0.0</v>
       </c>
       <c r="N51" s="2">
-        <v>779.0</v>
+        <v>782.0</v>
       </c>
       <c r="O51" s="2">
-        <v>366.0</v>
+        <v>368.0</v>
       </c>
       <c r="P51" s="2">
-        <v>413.0</v>
+        <v>414.0</v>
       </c>
       <c r="Q51" s="2">
         <v>0.0</v>
@@ -4077,7 +4077,7 @@
         <v>834.0</v>
       </c>
       <c r="J53" s="2">
-        <v>810.0</v>
+        <v>811.0</v>
       </c>
       <c r="K53" s="2">
         <v>1.0</v>
@@ -4089,7 +4089,7 @@
         <v>0.0</v>
       </c>
       <c r="N53" s="2">
-        <v>810.0</v>
+        <v>811.0</v>
       </c>
       <c r="O53" s="2">
         <v>447.0</v>
@@ -4098,7 +4098,7 @@
         <v>358.0</v>
       </c>
       <c r="Q53" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="R53" s="2">
         <v>6.0</v>
@@ -4290,7 +4290,7 @@
         <v>615.0</v>
       </c>
       <c r="J56" s="2">
-        <v>570.0</v>
+        <v>577.0</v>
       </c>
       <c r="K56" s="2">
         <v>1.0</v>
@@ -4302,10 +4302,10 @@
         <v>0.0</v>
       </c>
       <c r="N56" s="2">
-        <v>570.0</v>
+        <v>577.0</v>
       </c>
       <c r="O56" s="2">
-        <v>284.0</v>
+        <v>291.0</v>
       </c>
       <c r="P56" s="2">
         <v>286.0</v>
@@ -4314,7 +4314,7 @@
         <v>0.0</v>
       </c>
       <c r="R56" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S56" s="2">
         <v>0.0</v>
@@ -4329,7 +4329,7 @@
         <v>0.0</v>
       </c>
       <c r="W56" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
@@ -4361,7 +4361,7 @@
         <v>620.0</v>
       </c>
       <c r="J57" s="2">
-        <v>545.0</v>
+        <v>561.0</v>
       </c>
       <c r="K57" s="2">
         <v>1.0</v>
@@ -4373,10 +4373,10 @@
         <v>0.0</v>
       </c>
       <c r="N57" s="2">
-        <v>545.0</v>
+        <v>561.0</v>
       </c>
       <c r="O57" s="2">
-        <v>545.0</v>
+        <v>561.0</v>
       </c>
       <c r="P57" s="2">
         <v>0.0</v>
@@ -4574,7 +4574,7 @@
         <v>707.0</v>
       </c>
       <c r="J60" s="2">
-        <v>616.0</v>
+        <v>632.0</v>
       </c>
       <c r="K60" s="2">
         <v>1.0</v>
@@ -4586,13 +4586,13 @@
         <v>0.0</v>
       </c>
       <c r="N60" s="2">
-        <v>616.0</v>
+        <v>632.0</v>
       </c>
       <c r="O60" s="2">
-        <v>272.0</v>
+        <v>278.0</v>
       </c>
       <c r="P60" s="2">
-        <v>344.0</v>
+        <v>354.0</v>
       </c>
       <c r="Q60" s="2">
         <v>0.0</v>
@@ -4787,7 +4787,7 @@
         <v>1161.0</v>
       </c>
       <c r="J63" s="2">
-        <v>843.0</v>
+        <v>881.0</v>
       </c>
       <c r="K63" s="2">
         <v>1.0</v>
@@ -4799,19 +4799,19 @@
         <v>0.0</v>
       </c>
       <c r="N63" s="2">
-        <v>843.0</v>
+        <v>881.0</v>
       </c>
       <c r="O63" s="2">
-        <v>487.0</v>
+        <v>511.0</v>
       </c>
       <c r="P63" s="2">
-        <v>355.0</v>
+        <v>369.0</v>
       </c>
       <c r="Q63" s="2">
         <v>1.0</v>
       </c>
       <c r="R63" s="2">
-        <v>29.0</v>
+        <v>32.0</v>
       </c>
       <c r="S63" s="2">
         <v>1.0</v>
@@ -4826,7 +4826,7 @@
         <v>0.0</v>
       </c>
       <c r="W63" s="2">
-        <v>30.0</v>
+        <v>33.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
@@ -5000,7 +5000,7 @@
         <v>1155.0</v>
       </c>
       <c r="J66" s="2">
-        <v>1039.0</v>
+        <v>1044.0</v>
       </c>
       <c r="K66" s="2">
         <v>1.0</v>
@@ -5012,19 +5012,19 @@
         <v>0.0</v>
       </c>
       <c r="N66" s="2">
-        <v>1039.0</v>
+        <v>1044.0</v>
       </c>
       <c r="O66" s="2">
-        <v>564.0</v>
+        <v>567.0</v>
       </c>
       <c r="P66" s="2">
-        <v>473.0</v>
+        <v>475.0</v>
       </c>
       <c r="Q66" s="2">
         <v>2.0</v>
       </c>
       <c r="R66" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="S66" s="2">
         <v>51.0</v>
@@ -5039,7 +5039,7 @@
         <v>0.0</v>
       </c>
       <c r="W66" s="2">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
@@ -5166,7 +5166,7 @@
         <v>19.0</v>
       </c>
       <c r="R68" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="S68" s="2">
         <v>24.0</v>
@@ -5181,7 +5181,7 @@
         <v>0.0</v>
       </c>
       <c r="W68" s="2">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
@@ -5213,7 +5213,7 @@
         <v>1124.0</v>
       </c>
       <c r="J69" s="2">
-        <v>1007.0</v>
+        <v>1028.0</v>
       </c>
       <c r="K69" s="2">
         <v>1.0</v>
@@ -5225,13 +5225,13 @@
         <v>1.0</v>
       </c>
       <c r="N69" s="2">
-        <v>1006.0</v>
+        <v>1027.0</v>
       </c>
       <c r="O69" s="2">
-        <v>528.0</v>
+        <v>546.0</v>
       </c>
       <c r="P69" s="2">
-        <v>479.0</v>
+        <v>482.0</v>
       </c>
       <c r="Q69" s="2">
         <v>0.0</v>
@@ -5308,7 +5308,7 @@
         <v>10.0</v>
       </c>
       <c r="R70" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="S70" s="2">
         <v>1.0</v>
@@ -5317,13 +5317,13 @@
         <v>0.0</v>
       </c>
       <c r="U70" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="V70" s="2">
         <v>0.0</v>
       </c>
       <c r="W70" s="2">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
@@ -5710,7 +5710,7 @@
         <v>970.0</v>
       </c>
       <c r="J76" s="2">
-        <v>845.0</v>
+        <v>861.0</v>
       </c>
       <c r="K76" s="2">
         <v>1.0</v>
@@ -5722,13 +5722,13 @@
         <v>0.0</v>
       </c>
       <c r="N76" s="2">
-        <v>845.0</v>
+        <v>861.0</v>
       </c>
       <c r="O76" s="2">
-        <v>463.0</v>
+        <v>471.0</v>
       </c>
       <c r="P76" s="2">
-        <v>382.0</v>
+        <v>390.0</v>
       </c>
       <c r="Q76" s="2">
         <v>0.0</v>
@@ -5781,7 +5781,7 @@
         <v>792.0</v>
       </c>
       <c r="J77" s="2">
-        <v>571.0</v>
+        <v>583.0</v>
       </c>
       <c r="K77" s="2">
         <v>1.0</v>
@@ -5793,10 +5793,10 @@
         <v>0.0</v>
       </c>
       <c r="N77" s="2">
-        <v>571.0</v>
+        <v>583.0</v>
       </c>
       <c r="O77" s="2">
-        <v>106.0</v>
+        <v>118.0</v>
       </c>
       <c r="P77" s="2">
         <v>308.0</v>
@@ -5852,7 +5852,7 @@
         <v>1275.0</v>
       </c>
       <c r="J78" s="2">
-        <v>576.0</v>
+        <v>604.0</v>
       </c>
       <c r="K78" s="2">
         <v>1.0</v>
@@ -5864,13 +5864,13 @@
         <v>0.0</v>
       </c>
       <c r="N78" s="2">
-        <v>576.0</v>
+        <v>604.0</v>
       </c>
       <c r="O78" s="2">
-        <v>180.0</v>
+        <v>206.0</v>
       </c>
       <c r="P78" s="2">
-        <v>396.0</v>
+        <v>398.0</v>
       </c>
       <c r="Q78" s="2">
         <v>0.0</v>
@@ -6349,7 +6349,7 @@
         <v>1308.0</v>
       </c>
       <c r="J85" s="2">
-        <v>1122.0</v>
+        <v>1141.0</v>
       </c>
       <c r="K85" s="2">
         <v>1.0</v>
@@ -6361,16 +6361,16 @@
         <v>0.0</v>
       </c>
       <c r="N85" s="2">
-        <v>1122.0</v>
+        <v>1141.0</v>
       </c>
       <c r="O85" s="2">
-        <v>548.0</v>
+        <v>555.0</v>
       </c>
       <c r="P85" s="2">
-        <v>572.0</v>
+        <v>581.0</v>
       </c>
       <c r="Q85" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="R85" s="2">
         <v>42.0</v>
@@ -6379,7 +6379,7 @@
         <v>22.0</v>
       </c>
       <c r="T85" s="2">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="U85" s="2">
         <v>3.0</v>
@@ -6388,7 +6388,7 @@
         <v>0.0</v>
       </c>
       <c r="W85" s="2">
-        <v>67.0</v>
+        <v>74.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
@@ -6420,7 +6420,7 @@
         <v>1249.0</v>
       </c>
       <c r="J86" s="2">
-        <v>1032.0</v>
+        <v>1057.0</v>
       </c>
       <c r="K86" s="2">
         <v>1.0</v>
@@ -6432,13 +6432,13 @@
         <v>0.0</v>
       </c>
       <c r="N86" s="2">
-        <v>1032.0</v>
+        <v>1057.0</v>
       </c>
       <c r="O86" s="2">
-        <v>524.0</v>
+        <v>548.0</v>
       </c>
       <c r="P86" s="2">
-        <v>508.0</v>
+        <v>509.0</v>
       </c>
       <c r="Q86" s="2">
         <v>0.0</v>
@@ -6562,7 +6562,7 @@
         <v>882.0</v>
       </c>
       <c r="J88" s="2">
-        <v>655.0</v>
+        <v>656.0</v>
       </c>
       <c r="K88" s="2">
         <v>1.0</v>
@@ -6574,10 +6574,10 @@
         <v>0.0</v>
       </c>
       <c r="N88" s="2">
-        <v>655.0</v>
+        <v>656.0</v>
       </c>
       <c r="O88" s="2">
-        <v>326.0</v>
+        <v>327.0</v>
       </c>
       <c r="P88" s="2">
         <v>329.0</v>
@@ -6586,22 +6586,22 @@
         <v>0.0</v>
       </c>
       <c r="R88" s="2">
-        <v>0.0</v>
+        <v>28.0</v>
       </c>
       <c r="S88" s="2">
-        <v>0.0</v>
+        <v>26.0</v>
       </c>
       <c r="T88" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U88" s="2">
         <v>0.0</v>
       </c>
       <c r="V88" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="W88" s="2">
-        <v>0.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
@@ -6633,7 +6633,7 @@
         <v>814.0</v>
       </c>
       <c r="J89" s="2">
-        <v>566.0</v>
+        <v>579.0</v>
       </c>
       <c r="K89" s="2">
         <v>1.0</v>
@@ -6645,13 +6645,13 @@
         <v>0.0</v>
       </c>
       <c r="N89" s="2">
-        <v>566.0</v>
+        <v>579.0</v>
       </c>
       <c r="O89" s="2">
-        <v>296.0</v>
+        <v>306.0</v>
       </c>
       <c r="P89" s="2">
-        <v>270.0</v>
+        <v>273.0</v>
       </c>
       <c r="Q89" s="2">
         <v>0.0</v>
@@ -6775,7 +6775,7 @@
         <v>940.0</v>
       </c>
       <c r="J91" s="2">
-        <v>670.0</v>
+        <v>712.0</v>
       </c>
       <c r="K91" s="2">
         <v>1.0</v>
@@ -6787,16 +6787,16 @@
         <v>0.0</v>
       </c>
       <c r="N91" s="2">
-        <v>670.0</v>
+        <v>712.0</v>
       </c>
       <c r="O91" s="2">
-        <v>144.0</v>
+        <v>173.0</v>
       </c>
       <c r="P91" s="2">
-        <v>320.0</v>
+        <v>330.0</v>
       </c>
       <c r="Q91" s="2">
-        <v>206.0</v>
+        <v>209.0</v>
       </c>
       <c r="R91" s="2">
         <v>43.0</v>
@@ -6808,13 +6808,13 @@
         <v>2.0</v>
       </c>
       <c r="U91" s="2">
-        <v>126.0</v>
+        <v>127.0</v>
       </c>
       <c r="V91" s="2">
         <v>1.0</v>
       </c>
       <c r="W91" s="2">
-        <v>205.0</v>
+        <v>206.0</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
@@ -6846,7 +6846,7 @@
         <v>1315.0</v>
       </c>
       <c r="J92" s="2">
-        <v>691.0</v>
+        <v>704.0</v>
       </c>
       <c r="K92" s="2">
         <v>1.0</v>
@@ -6858,22 +6858,22 @@
         <v>0.0</v>
       </c>
       <c r="N92" s="2">
-        <v>691.0</v>
+        <v>704.0</v>
       </c>
       <c r="O92" s="2">
-        <v>298.0</v>
+        <v>306.0</v>
       </c>
       <c r="P92" s="2">
-        <v>296.0</v>
+        <v>299.0</v>
       </c>
       <c r="Q92" s="2">
-        <v>97.0</v>
+        <v>99.0</v>
       </c>
       <c r="R92" s="2">
         <v>48.0</v>
       </c>
       <c r="S92" s="2">
-        <v>95.0</v>
+        <v>97.0</v>
       </c>
       <c r="T92" s="2">
         <v>10.0</v>
@@ -6885,7 +6885,7 @@
         <v>2.0</v>
       </c>
       <c r="W92" s="2">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
@@ -6917,7 +6917,7 @@
         <v>960.0</v>
       </c>
       <c r="J93" s="2">
-        <v>810.0</v>
+        <v>817.0</v>
       </c>
       <c r="K93" s="2">
         <v>1.0</v>
@@ -6929,13 +6929,13 @@
         <v>0.0</v>
       </c>
       <c r="N93" s="2">
-        <v>810.0</v>
+        <v>817.0</v>
       </c>
       <c r="O93" s="2">
-        <v>469.0</v>
+        <v>473.0</v>
       </c>
       <c r="P93" s="2">
-        <v>340.0</v>
+        <v>343.0</v>
       </c>
       <c r="Q93" s="2">
         <v>1.0</v>
@@ -6988,7 +6988,7 @@
         <v>833.0</v>
       </c>
       <c r="J94" s="2">
-        <v>609.0</v>
+        <v>644.0</v>
       </c>
       <c r="K94" s="2">
         <v>1.0</v>
@@ -7000,13 +7000,13 @@
         <v>0.0</v>
       </c>
       <c r="N94" s="2">
-        <v>609.0</v>
+        <v>644.0</v>
       </c>
       <c r="O94" s="2">
-        <v>278.0</v>
+        <v>308.0</v>
       </c>
       <c r="P94" s="2">
-        <v>331.0</v>
+        <v>336.0</v>
       </c>
       <c r="Q94" s="2">
         <v>0.0</v>
@@ -7130,7 +7130,7 @@
         <v>1426.0</v>
       </c>
       <c r="J96" s="2">
-        <v>921.0</v>
+        <v>928.0</v>
       </c>
       <c r="K96" s="2">
         <v>1.0</v>
@@ -7142,13 +7142,13 @@
         <v>0.0</v>
       </c>
       <c r="N96" s="2">
-        <v>921.0</v>
+        <v>928.0</v>
       </c>
       <c r="O96" s="2">
-        <v>519.0</v>
+        <v>524.0</v>
       </c>
       <c r="P96" s="2">
-        <v>402.0</v>
+        <v>404.0</v>
       </c>
       <c r="Q96" s="2">
         <v>0.0</v>
@@ -7201,7 +7201,7 @@
         <v>1012.0</v>
       </c>
       <c r="J97" s="2">
-        <v>740.0</v>
+        <v>750.0</v>
       </c>
       <c r="K97" s="2">
         <v>1.0</v>
@@ -7213,13 +7213,13 @@
         <v>0.0</v>
       </c>
       <c r="N97" s="2">
-        <v>740.0</v>
+        <v>750.0</v>
       </c>
       <c r="O97" s="2">
-        <v>360.0</v>
+        <v>365.0</v>
       </c>
       <c r="P97" s="2">
-        <v>380.0</v>
+        <v>385.0</v>
       </c>
       <c r="Q97" s="2">
         <v>0.0</v>
@@ -7272,7 +7272,7 @@
         <v>1461.0</v>
       </c>
       <c r="J98" s="2">
-        <v>595.0</v>
+        <v>657.0</v>
       </c>
       <c r="K98" s="2">
         <v>1.0</v>
@@ -7284,13 +7284,13 @@
         <v>0.0</v>
       </c>
       <c r="N98" s="2">
-        <v>595.0</v>
+        <v>657.0</v>
       </c>
       <c r="O98" s="2">
-        <v>279.0</v>
+        <v>309.0</v>
       </c>
       <c r="P98" s="2">
-        <v>308.0</v>
+        <v>340.0</v>
       </c>
       <c r="Q98" s="2">
         <v>8.0</v>
@@ -7343,7 +7343,7 @@
         <v>878.0</v>
       </c>
       <c r="J99" s="2">
-        <v>755.0</v>
+        <v>756.0</v>
       </c>
       <c r="K99" s="2">
         <v>1.0</v>
@@ -7355,10 +7355,10 @@
         <v>0.0</v>
       </c>
       <c r="N99" s="2">
-        <v>755.0</v>
+        <v>756.0</v>
       </c>
       <c r="O99" s="2">
-        <v>389.0</v>
+        <v>390.0</v>
       </c>
       <c r="P99" s="2">
         <v>366.0</v>
@@ -7367,13 +7367,13 @@
         <v>0.0</v>
       </c>
       <c r="R99" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="S99" s="2">
         <v>0.0</v>
       </c>
       <c r="T99" s="2">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="U99" s="2">
         <v>0.0</v>
@@ -7382,7 +7382,7 @@
         <v>0.0</v>
       </c>
       <c r="W99" s="2">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
@@ -7414,7 +7414,7 @@
         <v>1254.0</v>
       </c>
       <c r="J100" s="2">
-        <v>1075.0</v>
+        <v>1090.0</v>
       </c>
       <c r="K100" s="2">
         <v>1.0</v>
@@ -7426,10 +7426,10 @@
         <v>0.0</v>
       </c>
       <c r="N100" s="2">
-        <v>1075.0</v>
+        <v>1090.0</v>
       </c>
       <c r="O100" s="2">
-        <v>470.0</v>
+        <v>485.0</v>
       </c>
       <c r="P100" s="2">
         <v>604.0</v>
@@ -7485,7 +7485,7 @@
         <v>1059.0</v>
       </c>
       <c r="J101" s="2">
-        <v>946.0</v>
+        <v>949.0</v>
       </c>
       <c r="K101" s="2">
         <v>1.0</v>
@@ -7497,22 +7497,22 @@
         <v>0.0</v>
       </c>
       <c r="N101" s="2">
-        <v>946.0</v>
+        <v>949.0</v>
       </c>
       <c r="O101" s="2">
-        <v>492.0</v>
+        <v>493.0</v>
       </c>
       <c r="P101" s="2">
-        <v>454.0</v>
+        <v>455.0</v>
       </c>
       <c r="Q101" s="2">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="R101" s="2">
         <v>46.0</v>
       </c>
       <c r="S101" s="2">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="T101" s="2">
         <v>2.0</v>
@@ -7524,7 +7524,7 @@
         <v>0.0</v>
       </c>
       <c r="W101" s="2">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
@@ -7556,7 +7556,7 @@
         <v>1159.0</v>
       </c>
       <c r="J102" s="2">
-        <v>922.0</v>
+        <v>943.0</v>
       </c>
       <c r="K102" s="2">
         <v>1.0</v>
@@ -7568,22 +7568,22 @@
         <v>0.0</v>
       </c>
       <c r="N102" s="2">
-        <v>922.0</v>
+        <v>943.0</v>
       </c>
       <c r="O102" s="2">
-        <v>466.0</v>
+        <v>479.0</v>
       </c>
       <c r="P102" s="2">
-        <v>456.0</v>
+        <v>464.0</v>
       </c>
       <c r="Q102" s="2">
         <v>0.0</v>
       </c>
       <c r="R102" s="2">
-        <v>52.0</v>
+        <v>54.0</v>
       </c>
       <c r="S102" s="2">
-        <v>52.0</v>
+        <v>60.0</v>
       </c>
       <c r="T102" s="2">
         <v>0.0</v>
@@ -7595,7 +7595,7 @@
         <v>0.0</v>
       </c>
       <c r="W102" s="2">
-        <v>104.0</v>
+        <v>114.0</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
@@ -7627,7 +7627,7 @@
         <v>663.0</v>
       </c>
       <c r="J103" s="2">
-        <v>504.0</v>
+        <v>507.0</v>
       </c>
       <c r="K103" s="2">
         <v>1.0</v>
@@ -7639,19 +7639,19 @@
         <v>0.0</v>
       </c>
       <c r="N103" s="2">
-        <v>504.0</v>
+        <v>507.0</v>
       </c>
       <c r="O103" s="2">
-        <v>283.0</v>
+        <v>285.0</v>
       </c>
       <c r="P103" s="2">
-        <v>221.0</v>
+        <v>222.0</v>
       </c>
       <c r="Q103" s="2">
         <v>0.0</v>
       </c>
       <c r="R103" s="2">
-        <v>4.0</v>
+        <v>22.0</v>
       </c>
       <c r="S103" s="2">
         <v>0.0</v>
@@ -7666,7 +7666,7 @@
         <v>0.0</v>
       </c>
       <c r="W103" s="2">
-        <v>4.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
@@ -7769,7 +7769,7 @@
         <v>1066.0</v>
       </c>
       <c r="J105" s="2">
-        <v>860.0</v>
+        <v>866.0</v>
       </c>
       <c r="K105" s="2">
         <v>1.0</v>
@@ -7781,22 +7781,22 @@
         <v>0.0</v>
       </c>
       <c r="N105" s="2">
-        <v>860.0</v>
+        <v>866.0</v>
       </c>
       <c r="O105" s="2">
-        <v>490.0</v>
+        <v>492.0</v>
       </c>
       <c r="P105" s="2">
         <v>370.0</v>
       </c>
       <c r="Q105" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="R105" s="2">
         <v>40.0</v>
       </c>
       <c r="S105" s="2">
-        <v>106.0</v>
+        <v>113.0</v>
       </c>
       <c r="T105" s="2">
         <v>0.0</v>
@@ -7808,7 +7808,7 @@
         <v>0.0</v>
       </c>
       <c r="W105" s="2">
-        <v>146.0</v>
+        <v>153.0</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -7840,7 +7840,7 @@
         <v>1098.0</v>
       </c>
       <c r="J106" s="2">
-        <v>870.0</v>
+        <v>912.0</v>
       </c>
       <c r="K106" s="2">
         <v>1.0</v>
@@ -7852,13 +7852,13 @@
         <v>0.0</v>
       </c>
       <c r="N106" s="2">
-        <v>870.0</v>
+        <v>912.0</v>
       </c>
       <c r="O106" s="2">
-        <v>400.0</v>
+        <v>437.0</v>
       </c>
       <c r="P106" s="2">
-        <v>457.0</v>
+        <v>462.0</v>
       </c>
       <c r="Q106" s="2">
         <v>13.0</v>
@@ -8053,7 +8053,7 @@
         <v>821.0</v>
       </c>
       <c r="J109" s="2">
-        <v>622.0</v>
+        <v>640.0</v>
       </c>
       <c r="K109" s="2">
         <v>1.0</v>
@@ -8065,13 +8065,13 @@
         <v>0.0</v>
       </c>
       <c r="N109" s="2">
-        <v>622.0</v>
+        <v>640.0</v>
       </c>
       <c r="O109" s="2">
-        <v>330.0</v>
+        <v>342.0</v>
       </c>
       <c r="P109" s="2">
-        <v>292.0</v>
+        <v>298.0</v>
       </c>
       <c r="Q109" s="2">
         <v>0.0</v>
@@ -8124,7 +8124,7 @@
         <v>754.0</v>
       </c>
       <c r="J110" s="2">
-        <v>492.0</v>
+        <v>501.0</v>
       </c>
       <c r="K110" s="2">
         <v>1.0</v>
@@ -8136,13 +8136,13 @@
         <v>0.0</v>
       </c>
       <c r="N110" s="2">
-        <v>492.0</v>
+        <v>501.0</v>
       </c>
       <c r="O110" s="2">
-        <v>238.0</v>
+        <v>245.0</v>
       </c>
       <c r="P110" s="2">
-        <v>254.0</v>
+        <v>256.0</v>
       </c>
       <c r="Q110" s="2">
         <v>0.0</v>
@@ -8195,7 +8195,7 @@
         <v>1027.0</v>
       </c>
       <c r="J111" s="2">
-        <v>819.0</v>
+        <v>850.0</v>
       </c>
       <c r="K111" s="2">
         <v>1.0</v>
@@ -8207,10 +8207,10 @@
         <v>0.0</v>
       </c>
       <c r="N111" s="2">
-        <v>819.0</v>
+        <v>850.0</v>
       </c>
       <c r="O111" s="2">
-        <v>385.0</v>
+        <v>416.0</v>
       </c>
       <c r="P111" s="2">
         <v>429.0</v>
@@ -8266,7 +8266,7 @@
         <v>709.0</v>
       </c>
       <c r="J112" s="2">
-        <v>556.0</v>
+        <v>565.0</v>
       </c>
       <c r="K112" s="2">
         <v>1.0</v>
@@ -8278,13 +8278,13 @@
         <v>0.0</v>
       </c>
       <c r="N112" s="2">
-        <v>556.0</v>
+        <v>565.0</v>
       </c>
       <c r="O112" s="2">
-        <v>284.0</v>
+        <v>291.0</v>
       </c>
       <c r="P112" s="2">
-        <v>268.0</v>
+        <v>270.0</v>
       </c>
       <c r="Q112" s="2">
         <v>4.0</v>
@@ -8296,7 +8296,7 @@
         <v>53.0</v>
       </c>
       <c r="T112" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U112" s="2">
         <v>1.0</v>
@@ -8305,7 +8305,7 @@
         <v>0.0</v>
       </c>
       <c r="W112" s="2">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
@@ -8337,7 +8337,7 @@
         <v>921.0</v>
       </c>
       <c r="J113" s="2">
-        <v>638.0</v>
+        <v>643.0</v>
       </c>
       <c r="K113" s="2">
         <v>1.0</v>
@@ -8349,10 +8349,10 @@
         <v>0.0</v>
       </c>
       <c r="N113" s="2">
-        <v>638.0</v>
+        <v>643.0</v>
       </c>
       <c r="O113" s="2">
-        <v>223.0</v>
+        <v>228.0</v>
       </c>
       <c r="P113" s="2">
         <v>415.0</v>
@@ -8408,7 +8408,7 @@
         <v>924.0</v>
       </c>
       <c r="J114" s="2">
-        <v>536.0</v>
+        <v>552.0</v>
       </c>
       <c r="K114" s="2">
         <v>1.0</v>
@@ -8420,19 +8420,19 @@
         <v>0.0</v>
       </c>
       <c r="N114" s="2">
-        <v>536.0</v>
+        <v>552.0</v>
       </c>
       <c r="O114" s="2">
-        <v>275.0</v>
+        <v>287.0</v>
       </c>
       <c r="P114" s="2">
-        <v>260.0</v>
+        <v>264.0</v>
       </c>
       <c r="Q114" s="2">
         <v>1.0</v>
       </c>
       <c r="R114" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="S114" s="2">
         <v>0.0</v>
@@ -8447,7 +8447,7 @@
         <v>0.0</v>
       </c>
       <c r="W114" s="2">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
@@ -8621,7 +8621,7 @@
         <v>1078.0</v>
       </c>
       <c r="J117" s="2">
-        <v>644.0</v>
+        <v>653.0</v>
       </c>
       <c r="K117" s="2">
         <v>1.0</v>
@@ -8633,13 +8633,13 @@
         <v>1.0</v>
       </c>
       <c r="N117" s="2">
-        <v>643.0</v>
+        <v>652.0</v>
       </c>
       <c r="O117" s="2">
-        <v>315.0</v>
+        <v>319.0</v>
       </c>
       <c r="P117" s="2">
-        <v>329.0</v>
+        <v>334.0</v>
       </c>
       <c r="Q117" s="2">
         <v>0.0</v>
@@ -8716,7 +8716,7 @@
         <v>4.0</v>
       </c>
       <c r="R118" s="2">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="S118" s="2">
         <v>10.0</v>
@@ -8731,7 +8731,7 @@
         <v>2.0</v>
       </c>
       <c r="W118" s="2">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
@@ -8763,7 +8763,7 @@
         <v>1084.0</v>
       </c>
       <c r="J119" s="2">
-        <v>681.0</v>
+        <v>682.0</v>
       </c>
       <c r="K119" s="2">
         <v>1.0</v>
@@ -8775,10 +8775,10 @@
         <v>0.0</v>
       </c>
       <c r="N119" s="2">
-        <v>681.0</v>
+        <v>682.0</v>
       </c>
       <c r="O119" s="2">
-        <v>400.0</v>
+        <v>401.0</v>
       </c>
       <c r="P119" s="2">
         <v>276.0</v>
@@ -8834,7 +8834,7 @@
         <v>971.0</v>
       </c>
       <c r="J120" s="2">
-        <v>588.0</v>
+        <v>595.0</v>
       </c>
       <c r="K120" s="2">
         <v>1.0</v>
@@ -8846,13 +8846,13 @@
         <v>0.0</v>
       </c>
       <c r="N120" s="2">
-        <v>588.0</v>
+        <v>595.0</v>
       </c>
       <c r="O120" s="2">
-        <v>299.0</v>
+        <v>304.0</v>
       </c>
       <c r="P120" s="2">
-        <v>286.0</v>
+        <v>288.0</v>
       </c>
       <c r="Q120" s="2">
         <v>3.0</v>
@@ -8905,7 +8905,7 @@
         <v>1425.0</v>
       </c>
       <c r="J121" s="2">
-        <v>633.0</v>
+        <v>634.0</v>
       </c>
       <c r="K121" s="2">
         <v>1.0</v>
@@ -8917,10 +8917,10 @@
         <v>0.0</v>
       </c>
       <c r="N121" s="2">
-        <v>633.0</v>
+        <v>634.0</v>
       </c>
       <c r="O121" s="2">
-        <v>389.0</v>
+        <v>390.0</v>
       </c>
       <c r="P121" s="2">
         <v>244.0</v>
@@ -8976,7 +8976,7 @@
         <v>939.0</v>
       </c>
       <c r="J122" s="2">
-        <v>575.0</v>
+        <v>604.0</v>
       </c>
       <c r="K122" s="2">
         <v>1.0</v>
@@ -8988,13 +8988,13 @@
         <v>4.0</v>
       </c>
       <c r="N122" s="2">
-        <v>571.0</v>
+        <v>600.0</v>
       </c>
       <c r="O122" s="2">
-        <v>324.0</v>
+        <v>337.0</v>
       </c>
       <c r="P122" s="2">
-        <v>236.0</v>
+        <v>252.0</v>
       </c>
       <c r="Q122" s="2">
         <v>15.0</v>
@@ -9047,7 +9047,7 @@
         <v>623.0</v>
       </c>
       <c r="J123" s="2">
-        <v>571.0</v>
+        <v>589.0</v>
       </c>
       <c r="K123" s="2">
         <v>1.0</v>
@@ -9059,22 +9059,22 @@
         <v>0.0</v>
       </c>
       <c r="N123" s="2">
-        <v>571.0</v>
+        <v>589.0</v>
       </c>
       <c r="O123" s="2">
-        <v>300.0</v>
+        <v>305.0</v>
       </c>
       <c r="P123" s="2">
-        <v>263.0</v>
+        <v>271.0</v>
       </c>
       <c r="Q123" s="2">
-        <v>8.0</v>
+        <v>13.0</v>
       </c>
       <c r="R123" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="S123" s="2">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="T123" s="2">
         <v>0.0</v>
@@ -9086,7 +9086,7 @@
         <v>0.0</v>
       </c>
       <c r="W123" s="2">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="124" ht="15.75" customHeight="1">
@@ -9260,7 +9260,7 @@
         <v>1151.0</v>
       </c>
       <c r="J126" s="2">
-        <v>833.0</v>
+        <v>850.0</v>
       </c>
       <c r="K126" s="2">
         <v>1.0</v>
@@ -9272,16 +9272,16 @@
         <v>0.0</v>
       </c>
       <c r="N126" s="2">
-        <v>833.0</v>
+        <v>850.0</v>
       </c>
       <c r="O126" s="2">
-        <v>433.0</v>
+        <v>443.0</v>
       </c>
       <c r="P126" s="2">
-        <v>383.0</v>
+        <v>389.0</v>
       </c>
       <c r="Q126" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R126" s="2">
         <v>9.0</v>
@@ -9331,7 +9331,7 @@
         <v>1150.0</v>
       </c>
       <c r="J127" s="2">
-        <v>818.0</v>
+        <v>823.0</v>
       </c>
       <c r="K127" s="2">
         <v>1.0</v>
@@ -9343,34 +9343,34 @@
         <v>0.0</v>
       </c>
       <c r="N127" s="2">
-        <v>818.0</v>
+        <v>823.0</v>
       </c>
       <c r="O127" s="2">
-        <v>524.0</v>
+        <v>527.0</v>
       </c>
       <c r="P127" s="2">
-        <v>294.0</v>
+        <v>296.0</v>
       </c>
       <c r="Q127" s="2">
         <v>0.0</v>
       </c>
       <c r="R127" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="S127" s="2">
         <v>20.0</v>
-      </c>
-      <c r="S127" s="2">
-        <v>18.0</v>
       </c>
       <c r="T127" s="2">
         <v>2.0</v>
       </c>
       <c r="U127" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="V127" s="2">
         <v>0.0</v>
       </c>
       <c r="W127" s="2">
-        <v>43.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -9402,7 +9402,7 @@
         <v>1267.0</v>
       </c>
       <c r="J128" s="2">
-        <v>938.0</v>
+        <v>954.0</v>
       </c>
       <c r="K128" s="2">
         <v>1.0</v>
@@ -9414,13 +9414,13 @@
         <v>0.0</v>
       </c>
       <c r="N128" s="2">
-        <v>938.0</v>
+        <v>954.0</v>
       </c>
       <c r="O128" s="2">
-        <v>522.0</v>
+        <v>531.0</v>
       </c>
       <c r="P128" s="2">
-        <v>414.0</v>
+        <v>421.0</v>
       </c>
       <c r="Q128" s="2">
         <v>2.0</v>
@@ -9429,19 +9429,19 @@
         <v>22.0</v>
       </c>
       <c r="S128" s="2">
-        <v>10.0</v>
+        <v>13.0</v>
       </c>
       <c r="T128" s="2">
         <v>0.0</v>
       </c>
       <c r="U128" s="2">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="V128" s="2">
         <v>0.0</v>
       </c>
       <c r="W128" s="2">
-        <v>38.0</v>
+        <v>51.0</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
@@ -9473,7 +9473,7 @@
         <v>1387.0</v>
       </c>
       <c r="J129" s="2">
-        <v>595.0</v>
+        <v>615.0</v>
       </c>
       <c r="K129" s="2">
         <v>1.0</v>
@@ -9485,19 +9485,19 @@
         <v>0.0</v>
       </c>
       <c r="N129" s="2">
-        <v>595.0</v>
+        <v>615.0</v>
       </c>
       <c r="O129" s="2">
-        <v>384.0</v>
+        <v>399.0</v>
       </c>
       <c r="P129" s="2">
-        <v>210.0</v>
+        <v>215.0</v>
       </c>
       <c r="Q129" s="2">
         <v>1.0</v>
       </c>
       <c r="R129" s="2">
-        <v>1.0</v>
+        <v>59.0</v>
       </c>
       <c r="S129" s="2">
         <v>1.0</v>
@@ -9512,7 +9512,7 @@
         <v>0.0</v>
       </c>
       <c r="W129" s="2">
-        <v>2.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="130" ht="15.75" customHeight="1">
@@ -9544,7 +9544,7 @@
         <v>808.0</v>
       </c>
       <c r="J130" s="2">
-        <v>603.0</v>
+        <v>604.0</v>
       </c>
       <c r="K130" s="2">
         <v>1.0</v>
@@ -9556,10 +9556,10 @@
         <v>2.0</v>
       </c>
       <c r="N130" s="2">
-        <v>601.0</v>
+        <v>602.0</v>
       </c>
       <c r="O130" s="2">
-        <v>393.0</v>
+        <v>394.0</v>
       </c>
       <c r="P130" s="2">
         <v>179.0</v>
@@ -9568,22 +9568,22 @@
         <v>31.0</v>
       </c>
       <c r="R130" s="2">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="S130" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="T130" s="2">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="U130" s="2">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="V130" s="2">
         <v>0.0</v>
       </c>
       <c r="W130" s="2">
-        <v>44.0</v>
+        <v>53.0</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
@@ -9615,7 +9615,7 @@
         <v>865.0</v>
       </c>
       <c r="J131" s="2">
-        <v>544.0</v>
+        <v>580.0</v>
       </c>
       <c r="K131" s="2">
         <v>1.0</v>
@@ -9627,16 +9627,16 @@
         <v>5.0</v>
       </c>
       <c r="N131" s="2">
-        <v>539.0</v>
+        <v>575.0</v>
       </c>
       <c r="O131" s="2">
-        <v>289.0</v>
+        <v>312.0</v>
       </c>
       <c r="P131" s="2">
-        <v>238.0</v>
+        <v>250.0</v>
       </c>
       <c r="Q131" s="2">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R131" s="2">
         <v>5.0</v>
@@ -9899,7 +9899,7 @@
         <v>1247.0</v>
       </c>
       <c r="J135" s="2">
-        <v>878.0</v>
+        <v>893.0</v>
       </c>
       <c r="K135" s="2">
         <v>1.0</v>
@@ -9911,13 +9911,13 @@
         <v>1.0</v>
       </c>
       <c r="N135" s="2">
-        <v>877.0</v>
+        <v>892.0</v>
       </c>
       <c r="O135" s="2">
-        <v>431.0</v>
+        <v>444.0</v>
       </c>
       <c r="P135" s="2">
-        <v>365.0</v>
+        <v>367.0</v>
       </c>
       <c r="Q135" s="2">
         <v>82.0</v>
@@ -9970,7 +9970,7 @@
         <v>1122.0</v>
       </c>
       <c r="J136" s="2">
-        <v>804.0</v>
+        <v>811.0</v>
       </c>
       <c r="K136" s="2">
         <v>1.0</v>
@@ -9982,13 +9982,13 @@
         <v>0.0</v>
       </c>
       <c r="N136" s="2">
-        <v>804.0</v>
+        <v>811.0</v>
       </c>
       <c r="O136" s="2">
-        <v>440.0</v>
+        <v>441.0</v>
       </c>
       <c r="P136" s="2">
-        <v>353.0</v>
+        <v>359.0</v>
       </c>
       <c r="Q136" s="2">
         <v>11.0</v>
@@ -10041,7 +10041,7 @@
         <v>1211.0</v>
       </c>
       <c r="J137" s="2">
-        <v>584.0</v>
+        <v>607.0</v>
       </c>
       <c r="K137" s="2">
         <v>1.0</v>
@@ -10053,22 +10053,22 @@
         <v>0.0</v>
       </c>
       <c r="N137" s="2">
-        <v>584.0</v>
+        <v>607.0</v>
       </c>
       <c r="O137" s="2">
-        <v>268.0</v>
+        <v>281.0</v>
       </c>
       <c r="P137" s="2">
-        <v>302.0</v>
+        <v>312.0</v>
       </c>
       <c r="Q137" s="2">
         <v>14.0</v>
       </c>
       <c r="R137" s="2">
-        <v>40.0</v>
+        <v>44.0</v>
       </c>
       <c r="S137" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="T137" s="2">
         <v>0.0</v>
@@ -10080,7 +10080,7 @@
         <v>0.0</v>
       </c>
       <c r="W137" s="2">
-        <v>56.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
@@ -10112,7 +10112,7 @@
         <v>1169.0</v>
       </c>
       <c r="J138" s="2">
-        <v>669.0</v>
+        <v>723.0</v>
       </c>
       <c r="K138" s="2">
         <v>1.0</v>
@@ -10124,13 +10124,13 @@
         <v>0.0</v>
       </c>
       <c r="N138" s="2">
-        <v>669.0</v>
+        <v>723.0</v>
       </c>
       <c r="O138" s="2">
-        <v>357.0</v>
+        <v>402.0</v>
       </c>
       <c r="P138" s="2">
-        <v>288.0</v>
+        <v>297.0</v>
       </c>
       <c r="Q138" s="2">
         <v>24.0</v>
@@ -10145,13 +10145,13 @@
         <v>1.0</v>
       </c>
       <c r="U138" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="V138" s="2">
         <v>0.0</v>
       </c>
       <c r="W138" s="2">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -10183,7 +10183,7 @@
         <v>1300.0</v>
       </c>
       <c r="J139" s="2">
-        <v>822.0</v>
+        <v>824.0</v>
       </c>
       <c r="K139" s="2">
         <v>1.0</v>
@@ -10195,10 +10195,10 @@
         <v>0.0</v>
       </c>
       <c r="N139" s="2">
-        <v>822.0</v>
+        <v>824.0</v>
       </c>
       <c r="O139" s="2">
-        <v>508.0</v>
+        <v>510.0</v>
       </c>
       <c r="P139" s="2">
         <v>293.0</v>
@@ -10254,7 +10254,7 @@
         <v>1236.0</v>
       </c>
       <c r="J140" s="2">
-        <v>647.0</v>
+        <v>660.0</v>
       </c>
       <c r="K140" s="2">
         <v>1.0</v>
@@ -10266,13 +10266,13 @@
         <v>0.0</v>
       </c>
       <c r="N140" s="2">
-        <v>647.0</v>
+        <v>660.0</v>
       </c>
       <c r="O140" s="2">
-        <v>324.0</v>
+        <v>336.0</v>
       </c>
       <c r="P140" s="2">
-        <v>322.0</v>
+        <v>323.0</v>
       </c>
       <c r="Q140" s="2">
         <v>1.0</v>
@@ -10396,7 +10396,7 @@
         <v>1047.0</v>
       </c>
       <c r="J142" s="2">
-        <v>897.0</v>
+        <v>911.0</v>
       </c>
       <c r="K142" s="2">
         <v>1.0</v>
@@ -10408,22 +10408,22 @@
         <v>0.0</v>
       </c>
       <c r="N142" s="2">
-        <v>897.0</v>
+        <v>911.0</v>
       </c>
       <c r="O142" s="2">
-        <v>506.0</v>
+        <v>508.0</v>
       </c>
       <c r="P142" s="2">
-        <v>391.0</v>
+        <v>399.0</v>
       </c>
       <c r="Q142" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="R142" s="2">
         <v>12.0</v>
       </c>
       <c r="S142" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="T142" s="2">
         <v>3.0</v>
@@ -10435,7 +10435,7 @@
         <v>0.0</v>
       </c>
       <c r="W142" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
@@ -10538,7 +10538,7 @@
         <v>1487.0</v>
       </c>
       <c r="J144" s="2">
-        <v>751.0</v>
+        <v>778.0</v>
       </c>
       <c r="K144" s="2">
         <v>1.0</v>
@@ -10550,13 +10550,13 @@
         <v>0.0</v>
       </c>
       <c r="N144" s="2">
-        <v>751.0</v>
+        <v>778.0</v>
       </c>
       <c r="O144" s="2">
-        <v>398.0</v>
+        <v>412.0</v>
       </c>
       <c r="P144" s="2">
-        <v>353.0</v>
+        <v>366.0</v>
       </c>
       <c r="Q144" s="2">
         <v>0.0</v>
@@ -10751,7 +10751,7 @@
         <v>1424.0</v>
       </c>
       <c r="J147" s="2">
-        <v>391.0</v>
+        <v>407.0</v>
       </c>
       <c r="K147" s="2">
         <v>1.0</v>
@@ -10763,16 +10763,16 @@
         <v>0.0</v>
       </c>
       <c r="N147" s="2">
-        <v>391.0</v>
+        <v>407.0</v>
       </c>
       <c r="O147" s="2">
-        <v>178.0</v>
+        <v>190.0</v>
       </c>
       <c r="P147" s="2">
-        <v>194.0</v>
+        <v>202.0</v>
       </c>
       <c r="Q147" s="2">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="R147" s="2">
         <v>5.0</v>
@@ -10893,7 +10893,7 @@
         <v>1218.0</v>
       </c>
       <c r="J149" s="2">
-        <v>548.0</v>
+        <v>574.0</v>
       </c>
       <c r="K149" s="2">
         <v>1.0</v>
@@ -10905,13 +10905,13 @@
         <v>0.0</v>
       </c>
       <c r="N149" s="2">
-        <v>548.0</v>
+        <v>574.0</v>
       </c>
       <c r="O149" s="2">
-        <v>323.0</v>
+        <v>336.0</v>
       </c>
       <c r="P149" s="2">
-        <v>221.0</v>
+        <v>234.0</v>
       </c>
       <c r="Q149" s="2">
         <v>4.0</v>
@@ -11035,7 +11035,7 @@
         <v>695.0</v>
       </c>
       <c r="J151" s="2">
-        <v>451.0</v>
+        <v>453.0</v>
       </c>
       <c r="K151" s="2">
         <v>1.0</v>
@@ -11047,13 +11047,13 @@
         <v>0.0</v>
       </c>
       <c r="N151" s="2">
-        <v>451.0</v>
+        <v>453.0</v>
       </c>
       <c r="O151" s="2">
         <v>221.0</v>
       </c>
       <c r="P151" s="2">
-        <v>230.0</v>
+        <v>232.0</v>
       </c>
       <c r="Q151" s="2">
         <v>0.0</v>
@@ -11485,7 +11485,7 @@
         <v>0.0</v>
       </c>
       <c r="R157" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="S157" s="2">
         <v>0.0</v>
@@ -11500,7 +11500,7 @@
         <v>0.0</v>
       </c>
       <c r="W157" s="2">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
@@ -11532,7 +11532,7 @@
         <v>1353.0</v>
       </c>
       <c r="J158" s="2">
-        <v>711.0</v>
+        <v>713.0</v>
       </c>
       <c r="K158" s="2">
         <v>1.0</v>
@@ -11544,10 +11544,10 @@
         <v>0.0</v>
       </c>
       <c r="N158" s="2">
-        <v>711.0</v>
+        <v>713.0</v>
       </c>
       <c r="O158" s="2">
-        <v>324.0</v>
+        <v>326.0</v>
       </c>
       <c r="P158" s="2">
         <v>387.0</v>
@@ -11603,7 +11603,7 @@
         <v>1153.0</v>
       </c>
       <c r="J159" s="2">
-        <v>802.0</v>
+        <v>804.0</v>
       </c>
       <c r="K159" s="2">
         <v>1.0</v>
@@ -11615,13 +11615,13 @@
         <v>1.0</v>
       </c>
       <c r="N159" s="2">
-        <v>801.0</v>
+        <v>803.0</v>
       </c>
       <c r="O159" s="2">
-        <v>450.0</v>
+        <v>451.0</v>
       </c>
       <c r="P159" s="2">
-        <v>352.0</v>
+        <v>353.0</v>
       </c>
       <c r="Q159" s="2">
         <v>0.0</v>
@@ -11745,7 +11745,7 @@
         <v>1401.0</v>
       </c>
       <c r="J161" s="2">
-        <v>899.0</v>
+        <v>900.0</v>
       </c>
       <c r="K161" s="2">
         <v>1.0</v>
@@ -11757,13 +11757,13 @@
         <v>0.0</v>
       </c>
       <c r="N161" s="2">
-        <v>899.0</v>
+        <v>900.0</v>
       </c>
       <c r="O161" s="2">
         <v>475.0</v>
       </c>
       <c r="P161" s="2">
-        <v>416.0</v>
+        <v>417.0</v>
       </c>
       <c r="Q161" s="2">
         <v>8.0</v>
@@ -11816,7 +11816,7 @@
         <v>1184.0</v>
       </c>
       <c r="J162" s="2">
-        <v>789.0</v>
+        <v>807.0</v>
       </c>
       <c r="K162" s="2">
         <v>1.0</v>
@@ -11828,16 +11828,16 @@
         <v>1.0</v>
       </c>
       <c r="N162" s="2">
-        <v>788.0</v>
+        <v>806.0</v>
       </c>
       <c r="O162" s="2">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="P162" s="2">
-        <v>184.0</v>
+        <v>186.0</v>
       </c>
       <c r="Q162" s="2">
-        <v>583.0</v>
+        <v>597.0</v>
       </c>
       <c r="R162" s="2">
         <v>0.0</v>
@@ -11887,7 +11887,7 @@
         <v>1298.0</v>
       </c>
       <c r="J163" s="2">
-        <v>701.0</v>
+        <v>716.0</v>
       </c>
       <c r="K163" s="2">
         <v>1.0</v>
@@ -11899,19 +11899,19 @@
         <v>0.0</v>
       </c>
       <c r="N163" s="2">
-        <v>701.0</v>
+        <v>716.0</v>
       </c>
       <c r="O163" s="2">
-        <v>12.0</v>
+        <v>19.0</v>
       </c>
       <c r="P163" s="2">
-        <v>313.0</v>
+        <v>320.0</v>
       </c>
       <c r="Q163" s="2">
-        <v>376.0</v>
+        <v>377.0</v>
       </c>
       <c r="R163" s="2">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="S163" s="2">
         <v>4.0</v>
@@ -11926,7 +11926,7 @@
         <v>0.0</v>
       </c>
       <c r="W163" s="2">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
@@ -11958,7 +11958,7 @@
         <v>1054.0</v>
       </c>
       <c r="J164" s="2">
-        <v>709.0</v>
+        <v>720.0</v>
       </c>
       <c r="K164" s="2">
         <v>1.0</v>
@@ -11970,16 +11970,16 @@
         <v>1.0</v>
       </c>
       <c r="N164" s="2">
-        <v>708.0</v>
+        <v>719.0</v>
       </c>
       <c r="O164" s="2">
-        <v>25.0</v>
+        <v>27.0</v>
       </c>
       <c r="P164" s="2">
-        <v>307.0</v>
+        <v>314.0</v>
       </c>
       <c r="Q164" s="2">
-        <v>377.0</v>
+        <v>379.0</v>
       </c>
       <c r="R164" s="2">
         <v>41.0</v>
@@ -12100,7 +12100,7 @@
         <v>932.0</v>
       </c>
       <c r="J166" s="2">
-        <v>619.0</v>
+        <v>629.0</v>
       </c>
       <c r="K166" s="2">
         <v>1.0</v>
@@ -12112,13 +12112,13 @@
         <v>0.0</v>
       </c>
       <c r="N166" s="2">
-        <v>619.0</v>
+        <v>629.0</v>
       </c>
       <c r="O166" s="2">
-        <v>340.0</v>
+        <v>349.0</v>
       </c>
       <c r="P166" s="2">
-        <v>279.0</v>
+        <v>280.0</v>
       </c>
       <c r="Q166" s="2">
         <v>0.0</v>
@@ -12313,7 +12313,7 @@
         <v>503.0</v>
       </c>
       <c r="J169" s="2">
-        <v>419.0</v>
+        <v>429.0</v>
       </c>
       <c r="K169" s="2">
         <v>1.0</v>
@@ -12325,13 +12325,13 @@
         <v>0.0</v>
       </c>
       <c r="N169" s="2">
-        <v>419.0</v>
+        <v>429.0</v>
       </c>
       <c r="O169" s="2">
-        <v>210.0</v>
+        <v>216.0</v>
       </c>
       <c r="P169" s="2">
-        <v>201.0</v>
+        <v>205.0</v>
       </c>
       <c r="Q169" s="2">
         <v>8.0</v>
@@ -12668,7 +12668,7 @@
         <v>1280.0</v>
       </c>
       <c r="J174" s="2">
-        <v>931.0</v>
+        <v>933.0</v>
       </c>
       <c r="K174" s="2">
         <v>1.0</v>
@@ -12680,10 +12680,10 @@
         <v>0.0</v>
       </c>
       <c r="N174" s="2">
-        <v>931.0</v>
+        <v>933.0</v>
       </c>
       <c r="O174" s="2">
-        <v>457.0</v>
+        <v>459.0</v>
       </c>
       <c r="P174" s="2">
         <v>474.0</v>
@@ -12739,7 +12739,7 @@
         <v>1257.0</v>
       </c>
       <c r="J175" s="2">
-        <v>893.0</v>
+        <v>948.0</v>
       </c>
       <c r="K175" s="2">
         <v>1.0</v>
@@ -12751,13 +12751,13 @@
         <v>0.0</v>
       </c>
       <c r="N175" s="2">
-        <v>893.0</v>
+        <v>948.0</v>
       </c>
       <c r="O175" s="2">
-        <v>421.0</v>
+        <v>445.0</v>
       </c>
       <c r="P175" s="2">
-        <v>472.0</v>
+        <v>503.0</v>
       </c>
       <c r="Q175" s="2">
         <v>0.0</v>
@@ -12810,7 +12810,7 @@
         <v>1045.0</v>
       </c>
       <c r="J176" s="2">
-        <v>502.0</v>
+        <v>523.0</v>
       </c>
       <c r="K176" s="2">
         <v>1.0</v>
@@ -12822,13 +12822,13 @@
         <v>0.0</v>
       </c>
       <c r="N176" s="2">
-        <v>502.0</v>
+        <v>523.0</v>
       </c>
       <c r="O176" s="2">
-        <v>206.0</v>
+        <v>217.0</v>
       </c>
       <c r="P176" s="2">
-        <v>295.0</v>
+        <v>305.0</v>
       </c>
       <c r="Q176" s="2">
         <v>1.0</v>
@@ -12837,19 +12837,19 @@
         <v>61.0</v>
       </c>
       <c r="S176" s="2">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="T176" s="2">
         <v>0.0</v>
       </c>
       <c r="U176" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="V176" s="2">
         <v>2.0</v>
       </c>
       <c r="W176" s="2">
-        <v>83.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -12881,7 +12881,7 @@
         <v>1075.0</v>
       </c>
       <c r="J177" s="2">
-        <v>469.0</v>
+        <v>489.0</v>
       </c>
       <c r="K177" s="2">
         <v>1.0</v>
@@ -12893,13 +12893,13 @@
         <v>0.0</v>
       </c>
       <c r="N177" s="2">
-        <v>469.0</v>
+        <v>489.0</v>
       </c>
       <c r="O177" s="2">
-        <v>245.0</v>
+        <v>264.0</v>
       </c>
       <c r="P177" s="2">
-        <v>224.0</v>
+        <v>225.0</v>
       </c>
       <c r="Q177" s="2">
         <v>0.0</v>
@@ -12952,7 +12952,7 @@
         <v>1008.0</v>
       </c>
       <c r="J178" s="2">
-        <v>408.0</v>
+        <v>418.0</v>
       </c>
       <c r="K178" s="2">
         <v>1.0</v>
@@ -12964,13 +12964,13 @@
         <v>0.0</v>
       </c>
       <c r="N178" s="2">
-        <v>408.0</v>
+        <v>418.0</v>
       </c>
       <c r="O178" s="2">
-        <v>174.0</v>
+        <v>178.0</v>
       </c>
       <c r="P178" s="2">
-        <v>233.0</v>
+        <v>239.0</v>
       </c>
       <c r="Q178" s="2">
         <v>1.0</v>
@@ -13023,7 +13023,7 @@
         <v>1061.0</v>
       </c>
       <c r="J179" s="2">
-        <v>602.0</v>
+        <v>628.0</v>
       </c>
       <c r="K179" s="2">
         <v>1.0</v>
@@ -13035,19 +13035,19 @@
         <v>0.0</v>
       </c>
       <c r="N179" s="2">
-        <v>602.0</v>
+        <v>628.0</v>
       </c>
       <c r="O179" s="2">
-        <v>367.0</v>
+        <v>385.0</v>
       </c>
       <c r="P179" s="2">
-        <v>234.0</v>
+        <v>242.0</v>
       </c>
       <c r="Q179" s="2">
         <v>1.0</v>
       </c>
       <c r="R179" s="2">
-        <v>41.0</v>
+        <v>46.0</v>
       </c>
       <c r="S179" s="2">
         <v>7.0</v>
@@ -13062,7 +13062,7 @@
         <v>0.0</v>
       </c>
       <c r="W179" s="2">
-        <v>62.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
@@ -13094,7 +13094,7 @@
         <v>781.0</v>
       </c>
       <c r="J180" s="2">
-        <v>396.0</v>
+        <v>409.0</v>
       </c>
       <c r="K180" s="2">
         <v>1.0</v>
@@ -13106,13 +13106,13 @@
         <v>0.0</v>
       </c>
       <c r="N180" s="2">
-        <v>396.0</v>
+        <v>409.0</v>
       </c>
       <c r="O180" s="2">
-        <v>209.0</v>
+        <v>216.0</v>
       </c>
       <c r="P180" s="2">
-        <v>187.0</v>
+        <v>193.0</v>
       </c>
       <c r="Q180" s="2">
         <v>0.0</v>
@@ -13165,7 +13165,7 @@
         <v>855.0</v>
       </c>
       <c r="J181" s="2">
-        <v>398.0</v>
+        <v>405.0</v>
       </c>
       <c r="K181" s="2">
         <v>1.0</v>
@@ -13177,13 +13177,13 @@
         <v>0.0</v>
       </c>
       <c r="N181" s="2">
-        <v>398.0</v>
+        <v>405.0</v>
       </c>
       <c r="O181" s="2">
-        <v>210.0</v>
+        <v>214.0</v>
       </c>
       <c r="P181" s="2">
-        <v>188.0</v>
+        <v>191.0</v>
       </c>
       <c r="Q181" s="2">
         <v>0.0</v>
@@ -13520,7 +13520,7 @@
         <v>1067.0</v>
       </c>
       <c r="J186" s="2">
-        <v>704.0</v>
+        <v>767.0</v>
       </c>
       <c r="K186" s="2">
         <v>1.0</v>
@@ -13532,13 +13532,13 @@
         <v>0.0</v>
       </c>
       <c r="N186" s="2">
-        <v>704.0</v>
+        <v>767.0</v>
       </c>
       <c r="O186" s="2">
-        <v>143.0</v>
+        <v>185.0</v>
       </c>
       <c r="P186" s="2">
-        <v>307.0</v>
+        <v>328.0</v>
       </c>
       <c r="Q186" s="2">
         <v>254.0</v>
@@ -13662,7 +13662,7 @@
         <v>1017.0</v>
       </c>
       <c r="J188" s="2">
-        <v>643.0</v>
+        <v>657.0</v>
       </c>
       <c r="K188" s="2">
         <v>1.0</v>
@@ -13674,13 +13674,13 @@
         <v>0.0</v>
       </c>
       <c r="N188" s="2">
-        <v>643.0</v>
+        <v>657.0</v>
       </c>
       <c r="O188" s="2">
-        <v>237.0</v>
+        <v>250.0</v>
       </c>
       <c r="P188" s="2">
-        <v>348.0</v>
+        <v>349.0</v>
       </c>
       <c r="Q188" s="2">
         <v>58.0</v>
@@ -13689,7 +13689,7 @@
         <v>70.0</v>
       </c>
       <c r="S188" s="2">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="T188" s="2">
         <v>0.0</v>
@@ -13701,7 +13701,7 @@
         <v>0.0</v>
       </c>
       <c r="W188" s="2">
-        <v>89.0</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="189" ht="15.75" customHeight="1">
@@ -13733,7 +13733,7 @@
         <v>1282.0</v>
       </c>
       <c r="J189" s="2">
-        <v>720.0</v>
+        <v>740.0</v>
       </c>
       <c r="K189" s="2">
         <v>1.0</v>
@@ -13745,13 +13745,13 @@
         <v>0.0</v>
       </c>
       <c r="N189" s="2">
-        <v>720.0</v>
+        <v>740.0</v>
       </c>
       <c r="O189" s="2">
-        <v>202.0</v>
+        <v>216.0</v>
       </c>
       <c r="P189" s="2">
-        <v>248.0</v>
+        <v>254.0</v>
       </c>
       <c r="Q189" s="2">
         <v>270.0</v>
@@ -13804,7 +13804,7 @@
         <v>1393.0</v>
       </c>
       <c r="J190" s="2">
-        <v>912.0</v>
+        <v>922.0</v>
       </c>
       <c r="K190" s="2">
         <v>1.0</v>
@@ -13816,10 +13816,10 @@
         <v>0.0</v>
       </c>
       <c r="N190" s="2">
-        <v>912.0</v>
+        <v>922.0</v>
       </c>
       <c r="O190" s="2">
-        <v>515.0</v>
+        <v>525.0</v>
       </c>
       <c r="P190" s="2">
         <v>376.0</v>
@@ -13946,7 +13946,7 @@
         <v>508.0</v>
       </c>
       <c r="J192" s="2">
-        <v>358.0</v>
+        <v>378.0</v>
       </c>
       <c r="K192" s="2">
         <v>1.0</v>
@@ -13958,13 +13958,13 @@
         <v>0.0</v>
       </c>
       <c r="N192" s="2">
-        <v>358.0</v>
+        <v>378.0</v>
       </c>
       <c r="O192" s="2">
-        <v>203.0</v>
+        <v>221.0</v>
       </c>
       <c r="P192" s="2">
-        <v>153.0</v>
+        <v>155.0</v>
       </c>
       <c r="Q192" s="2">
         <v>2.0</v>
@@ -13976,7 +13976,7 @@
         <v>2.0</v>
       </c>
       <c r="T192" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="U192" s="2">
         <v>0.0</v>
@@ -13985,7 +13985,7 @@
         <v>0.0</v>
       </c>
       <c r="W192" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
@@ -14230,7 +14230,7 @@
         <v>1391.0</v>
       </c>
       <c r="J196" s="2">
-        <v>1129.0</v>
+        <v>1243.0</v>
       </c>
       <c r="K196" s="2">
         <v>1.0</v>
@@ -14242,25 +14242,25 @@
         <v>0.0</v>
       </c>
       <c r="N196" s="2">
-        <v>1129.0</v>
+        <v>1243.0</v>
       </c>
       <c r="O196" s="2">
-        <v>437.0</v>
+        <v>508.0</v>
       </c>
       <c r="P196" s="2">
-        <v>494.0</v>
+        <v>537.0</v>
       </c>
       <c r="Q196" s="2">
         <v>198.0</v>
       </c>
       <c r="R196" s="2">
-        <v>0.0</v>
+        <v>22.0</v>
       </c>
       <c r="S196" s="2">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="T196" s="2">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="U196" s="2">
         <v>0.0</v>
@@ -14269,7 +14269,7 @@
         <v>0.0</v>
       </c>
       <c r="W196" s="2">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1">
@@ -14301,7 +14301,7 @@
         <v>1163.0</v>
       </c>
       <c r="J197" s="2">
-        <v>1063.0</v>
+        <v>1066.0</v>
       </c>
       <c r="K197" s="2">
         <v>1.0</v>
@@ -14313,13 +14313,13 @@
         <v>0.0</v>
       </c>
       <c r="N197" s="2">
-        <v>1063.0</v>
+        <v>1066.0</v>
       </c>
       <c r="O197" s="2">
-        <v>596.0</v>
+        <v>598.0</v>
       </c>
       <c r="P197" s="2">
-        <v>349.0</v>
+        <v>350.0</v>
       </c>
       <c r="Q197" s="2">
         <v>118.0</v>
@@ -14328,10 +14328,10 @@
         <v>28.0</v>
       </c>
       <c r="S197" s="2">
-        <v>22.0</v>
+        <v>27.0</v>
       </c>
       <c r="T197" s="2">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="U197" s="2">
         <v>0.0</v>
@@ -14340,7 +14340,7 @@
         <v>0.0</v>
       </c>
       <c r="W197" s="2">
-        <v>54.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
@@ -14514,7 +14514,7 @@
         <v>704.0</v>
       </c>
       <c r="J200" s="2">
-        <v>493.0</v>
+        <v>503.0</v>
       </c>
       <c r="K200" s="2">
         <v>1.0</v>
@@ -14526,13 +14526,13 @@
         <v>0.0</v>
       </c>
       <c r="N200" s="2">
-        <v>493.0</v>
+        <v>503.0</v>
       </c>
       <c r="O200" s="2">
-        <v>304.0</v>
+        <v>305.0</v>
       </c>
       <c r="P200" s="2">
-        <v>186.0</v>
+        <v>195.0</v>
       </c>
       <c r="Q200" s="2">
         <v>3.0</v>
@@ -14656,7 +14656,7 @@
         <v>1172.0</v>
       </c>
       <c r="J202" s="2">
-        <v>576.0</v>
+        <v>615.0</v>
       </c>
       <c r="K202" s="2">
         <v>1.0</v>
@@ -14668,13 +14668,13 @@
         <v>0.0</v>
       </c>
       <c r="N202" s="2">
-        <v>576.0</v>
+        <v>615.0</v>
       </c>
       <c r="O202" s="2">
-        <v>327.0</v>
+        <v>357.0</v>
       </c>
       <c r="P202" s="2">
-        <v>249.0</v>
+        <v>258.0</v>
       </c>
       <c r="Q202" s="2">
         <v>0.0</v>
@@ -14727,7 +14727,7 @@
         <v>1257.0</v>
       </c>
       <c r="J203" s="2">
-        <v>713.0</v>
+        <v>714.0</v>
       </c>
       <c r="K203" s="2">
         <v>1.0</v>
@@ -14739,10 +14739,10 @@
         <v>0.0</v>
       </c>
       <c r="N203" s="2">
-        <v>713.0</v>
+        <v>714.0</v>
       </c>
       <c r="O203" s="2">
-        <v>404.0</v>
+        <v>405.0</v>
       </c>
       <c r="P203" s="2">
         <v>309.0</v>
@@ -14751,13 +14751,13 @@
         <v>0.0</v>
       </c>
       <c r="R203" s="2">
-        <v>43.0</v>
+        <v>53.0</v>
       </c>
       <c r="S203" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="T203" s="2">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="U203" s="2">
         <v>0.0</v>
@@ -14766,7 +14766,7 @@
         <v>0.0</v>
       </c>
       <c r="W203" s="2">
-        <v>43.0</v>
+        <v>61.0</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
@@ -14798,7 +14798,7 @@
         <v>1235.0</v>
       </c>
       <c r="J204" s="2">
-        <v>642.0</v>
+        <v>657.0</v>
       </c>
       <c r="K204" s="2">
         <v>1.0</v>
@@ -14810,13 +14810,13 @@
         <v>0.0</v>
       </c>
       <c r="N204" s="2">
-        <v>642.0</v>
+        <v>657.0</v>
       </c>
       <c r="O204" s="2">
-        <v>353.0</v>
+        <v>360.0</v>
       </c>
       <c r="P204" s="2">
-        <v>283.0</v>
+        <v>291.0</v>
       </c>
       <c r="Q204" s="2">
         <v>6.0</v>
@@ -14869,7 +14869,7 @@
         <v>897.0</v>
       </c>
       <c r="J205" s="2">
-        <v>486.0</v>
+        <v>497.0</v>
       </c>
       <c r="K205" s="2">
         <v>1.0</v>
@@ -14881,13 +14881,13 @@
         <v>0.0</v>
       </c>
       <c r="N205" s="2">
-        <v>486.0</v>
+        <v>497.0</v>
       </c>
       <c r="O205" s="2">
-        <v>235.0</v>
+        <v>241.0</v>
       </c>
       <c r="P205" s="2">
-        <v>217.0</v>
+        <v>222.0</v>
       </c>
       <c r="Q205" s="2">
         <v>34.0</v>
@@ -14940,7 +14940,7 @@
         <v>859.0</v>
       </c>
       <c r="J206" s="2">
-        <v>660.0</v>
+        <v>675.0</v>
       </c>
       <c r="K206" s="2">
         <v>1.0</v>
@@ -14952,10 +14952,10 @@
         <v>0.0</v>
       </c>
       <c r="N206" s="2">
-        <v>660.0</v>
+        <v>675.0</v>
       </c>
       <c r="O206" s="2">
-        <v>401.0</v>
+        <v>416.0</v>
       </c>
       <c r="P206" s="2">
         <v>259.0</v>
@@ -15011,7 +15011,7 @@
         <v>943.0</v>
       </c>
       <c r="J207" s="2">
-        <v>490.0</v>
+        <v>506.0</v>
       </c>
       <c r="K207" s="2">
         <v>1.0</v>
@@ -15023,13 +15023,13 @@
         <v>0.0</v>
       </c>
       <c r="N207" s="2">
-        <v>490.0</v>
+        <v>506.0</v>
       </c>
       <c r="O207" s="2">
-        <v>282.0</v>
+        <v>286.0</v>
       </c>
       <c r="P207" s="2">
-        <v>204.0</v>
+        <v>216.0</v>
       </c>
       <c r="Q207" s="2">
         <v>4.0</v>
@@ -15082,7 +15082,7 @@
         <v>762.0</v>
       </c>
       <c r="J208" s="2">
-        <v>510.0</v>
+        <v>534.0</v>
       </c>
       <c r="K208" s="2">
         <v>1.0</v>
@@ -15094,22 +15094,22 @@
         <v>0.0</v>
       </c>
       <c r="N208" s="2">
-        <v>510.0</v>
+        <v>534.0</v>
       </c>
       <c r="O208" s="2">
-        <v>132.0</v>
+        <v>146.0</v>
       </c>
       <c r="P208" s="2">
-        <v>222.0</v>
+        <v>231.0</v>
       </c>
       <c r="Q208" s="2">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="R208" s="2">
         <v>0.0</v>
       </c>
       <c r="S208" s="2">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="T208" s="2">
         <v>1.0</v>
@@ -15121,7 +15121,7 @@
         <v>0.0</v>
       </c>
       <c r="W208" s="2">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="209" ht="15.75" customHeight="1">
@@ -15153,7 +15153,7 @@
         <v>951.0</v>
       </c>
       <c r="J209" s="2">
-        <v>827.0</v>
+        <v>833.0</v>
       </c>
       <c r="K209" s="2">
         <v>1.0</v>
@@ -15165,22 +15165,22 @@
         <v>0.0</v>
       </c>
       <c r="N209" s="2">
-        <v>827.0</v>
+        <v>833.0</v>
       </c>
       <c r="O209" s="2">
         <v>432.0</v>
       </c>
       <c r="P209" s="2">
-        <v>395.0</v>
+        <v>401.0</v>
       </c>
       <c r="Q209" s="2">
         <v>0.0</v>
       </c>
       <c r="R209" s="2">
-        <v>44.0</v>
+        <v>46.0</v>
       </c>
       <c r="S209" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="T209" s="2">
         <v>2.0</v>
@@ -15192,7 +15192,7 @@
         <v>0.0</v>
       </c>
       <c r="W209" s="2">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
     </row>
     <row r="210" ht="15.75" customHeight="1">
@@ -15437,7 +15437,7 @@
         <v>1034.0</v>
       </c>
       <c r="J213" s="2">
-        <v>660.0</v>
+        <v>687.0</v>
       </c>
       <c r="K213" s="2">
         <v>1.0</v>
@@ -15449,13 +15449,13 @@
         <v>0.0</v>
       </c>
       <c r="N213" s="2">
-        <v>660.0</v>
+        <v>687.0</v>
       </c>
       <c r="O213" s="2">
-        <v>338.0</v>
+        <v>359.0</v>
       </c>
       <c r="P213" s="2">
-        <v>322.0</v>
+        <v>328.0</v>
       </c>
       <c r="Q213" s="2">
         <v>0.0</v>
@@ -15579,7 +15579,7 @@
         <v>1067.0</v>
       </c>
       <c r="J215" s="2">
-        <v>720.0</v>
+        <v>796.0</v>
       </c>
       <c r="K215" s="2">
         <v>1.0</v>
@@ -15591,13 +15591,13 @@
         <v>0.0</v>
       </c>
       <c r="N215" s="2">
-        <v>720.0</v>
+        <v>796.0</v>
       </c>
       <c r="O215" s="2">
-        <v>304.0</v>
+        <v>364.0</v>
       </c>
       <c r="P215" s="2">
-        <v>416.0</v>
+        <v>432.0</v>
       </c>
       <c r="Q215" s="2">
         <v>0.0</v>
@@ -15606,10 +15606,10 @@
         <v>12.0</v>
       </c>
       <c r="S215" s="2">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="T215" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="U215" s="2">
         <v>1.0</v>
@@ -15618,7 +15618,7 @@
         <v>0.0</v>
       </c>
       <c r="W215" s="2">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="216" ht="15.75" customHeight="1">
@@ -15816,10 +15816,10 @@
         <v>0.0</v>
       </c>
       <c r="R218" s="2">
-        <v>24.0</v>
+        <v>33.0</v>
       </c>
       <c r="S218" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="T218" s="2">
         <v>1.0</v>
@@ -15831,7 +15831,7 @@
         <v>0.0</v>
       </c>
       <c r="W218" s="2">
-        <v>33.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="219" ht="15.75" customHeight="1">
@@ -15863,7 +15863,7 @@
         <v>1433.0</v>
       </c>
       <c r="J219" s="2">
-        <v>856.0</v>
+        <v>867.0</v>
       </c>
       <c r="K219" s="2">
         <v>1.0</v>
@@ -15875,22 +15875,22 @@
         <v>0.0</v>
       </c>
       <c r="N219" s="2">
-        <v>856.0</v>
+        <v>867.0</v>
       </c>
       <c r="O219" s="2">
-        <v>115.0</v>
+        <v>121.0</v>
       </c>
       <c r="P219" s="2">
-        <v>369.0</v>
+        <v>372.0</v>
       </c>
       <c r="Q219" s="2">
-        <v>372.0</v>
+        <v>374.0</v>
       </c>
       <c r="R219" s="2">
         <v>22.0</v>
       </c>
       <c r="S219" s="2">
-        <v>26.0</v>
+        <v>32.0</v>
       </c>
       <c r="T219" s="2">
         <v>3.0</v>
@@ -15902,7 +15902,7 @@
         <v>0.0</v>
       </c>
       <c r="W219" s="2">
-        <v>52.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="220" ht="15.75" customHeight="1">
@@ -16076,7 +16076,7 @@
         <v>1043.0</v>
       </c>
       <c r="J222" s="2">
-        <v>629.0</v>
+        <v>652.0</v>
       </c>
       <c r="K222" s="2">
         <v>1.0</v>
@@ -16088,13 +16088,13 @@
         <v>0.0</v>
       </c>
       <c r="N222" s="2">
-        <v>629.0</v>
+        <v>652.0</v>
       </c>
       <c r="O222" s="2">
-        <v>126.0</v>
+        <v>140.0</v>
       </c>
       <c r="P222" s="2">
-        <v>267.0</v>
+        <v>276.0</v>
       </c>
       <c r="Q222" s="2">
         <v>236.0</v>
@@ -16147,7 +16147,7 @@
         <v>1272.0</v>
       </c>
       <c r="J223" s="2">
-        <v>768.0</v>
+        <v>769.0</v>
       </c>
       <c r="K223" s="2">
         <v>1.0</v>
@@ -16159,7 +16159,7 @@
         <v>0.0</v>
       </c>
       <c r="N223" s="2">
-        <v>768.0</v>
+        <v>769.0</v>
       </c>
       <c r="O223" s="2">
         <v>94.0</v>
@@ -16168,7 +16168,7 @@
         <v>263.0</v>
       </c>
       <c r="Q223" s="2">
-        <v>411.0</v>
+        <v>412.0</v>
       </c>
       <c r="R223" s="2">
         <v>54.0</v>
@@ -16218,7 +16218,7 @@
         <v>766.0</v>
       </c>
       <c r="J224" s="2">
-        <v>486.0</v>
+        <v>497.0</v>
       </c>
       <c r="K224" s="2">
         <v>1.0</v>
@@ -16230,16 +16230,16 @@
         <v>0.0</v>
       </c>
       <c r="N224" s="2">
-        <v>486.0</v>
+        <v>497.0</v>
       </c>
       <c r="O224" s="2">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="P224" s="2">
         <v>38.0</v>
       </c>
       <c r="Q224" s="2">
-        <v>427.0</v>
+        <v>437.0</v>
       </c>
       <c r="R224" s="2">
         <v>1.0</v>
@@ -16360,7 +16360,7 @@
         <v>1256.0</v>
       </c>
       <c r="J226" s="2">
-        <v>746.0</v>
+        <v>747.0</v>
       </c>
       <c r="K226" s="2">
         <v>1.0</v>
@@ -16372,10 +16372,10 @@
         <v>0.0</v>
       </c>
       <c r="N226" s="2">
-        <v>746.0</v>
+        <v>747.0</v>
       </c>
       <c r="O226" s="2">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="P226" s="2">
         <v>342.0</v>
@@ -16384,7 +16384,7 @@
         <v>323.0</v>
       </c>
       <c r="R226" s="2">
-        <v>123.0</v>
+        <v>126.0</v>
       </c>
       <c r="S226" s="2">
         <v>21.0</v>
@@ -16399,7 +16399,7 @@
         <v>0.0</v>
       </c>
       <c r="W226" s="2">
-        <v>144.0</v>
+        <v>147.0</v>
       </c>
     </row>
     <row r="227" ht="15.75" customHeight="1">
@@ -16431,7 +16431,7 @@
         <v>428.0</v>
       </c>
       <c r="J227" s="2">
-        <v>244.0</v>
+        <v>254.0</v>
       </c>
       <c r="K227" s="2">
         <v>1.0</v>
@@ -16443,19 +16443,19 @@
         <v>0.0</v>
       </c>
       <c r="N227" s="2">
-        <v>244.0</v>
+        <v>254.0</v>
       </c>
       <c r="O227" s="2">
-        <v>145.0</v>
+        <v>154.0</v>
       </c>
       <c r="P227" s="2">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="Q227" s="2">
         <v>0.0</v>
       </c>
       <c r="R227" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="S227" s="2">
         <v>2.0</v>
@@ -16470,7 +16470,7 @@
         <v>0.0</v>
       </c>
       <c r="W227" s="2">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="228" ht="15.75" customHeight="1">
@@ -16573,7 +16573,7 @@
         <v>832.0</v>
       </c>
       <c r="J229" s="2">
-        <v>779.0</v>
+        <v>781.0</v>
       </c>
       <c r="K229" s="2">
         <v>1.0</v>
@@ -16585,10 +16585,10 @@
         <v>0.0</v>
       </c>
       <c r="N229" s="2">
-        <v>779.0</v>
+        <v>781.0</v>
       </c>
       <c r="O229" s="2">
-        <v>443.0</v>
+        <v>445.0</v>
       </c>
       <c r="P229" s="2">
         <v>336.0</v>
@@ -16644,7 +16644,7 @@
         <v>934.0</v>
       </c>
       <c r="J230" s="2">
-        <v>555.0</v>
+        <v>560.0</v>
       </c>
       <c r="K230" s="2">
         <v>1.0</v>
@@ -16656,13 +16656,13 @@
         <v>0.0</v>
       </c>
       <c r="N230" s="2">
-        <v>555.0</v>
+        <v>560.0</v>
       </c>
       <c r="O230" s="2">
         <v>112.0</v>
       </c>
       <c r="P230" s="2">
-        <v>251.0</v>
+        <v>256.0</v>
       </c>
       <c r="Q230" s="2">
         <v>192.0</v>
@@ -16715,7 +16715,7 @@
         <v>1070.0</v>
       </c>
       <c r="J231" s="2">
-        <v>762.0</v>
+        <v>767.0</v>
       </c>
       <c r="K231" s="2">
         <v>1.0</v>
@@ -16727,10 +16727,10 @@
         <v>0.0</v>
       </c>
       <c r="N231" s="2">
-        <v>762.0</v>
+        <v>767.0</v>
       </c>
       <c r="O231" s="2">
-        <v>396.0</v>
+        <v>401.0</v>
       </c>
       <c r="P231" s="2">
         <v>345.0</v>
@@ -16739,10 +16739,10 @@
         <v>21.0</v>
       </c>
       <c r="R231" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="S231" s="2">
-        <v>64.0</v>
+        <v>70.0</v>
       </c>
       <c r="T231" s="2">
         <v>1.0</v>
@@ -16754,7 +16754,7 @@
         <v>0.0</v>
       </c>
       <c r="W231" s="2">
-        <v>79.0</v>
+        <v>86.0</v>
       </c>
     </row>
     <row r="232" ht="15.75" customHeight="1">
@@ -16786,7 +16786,7 @@
         <v>1369.0</v>
       </c>
       <c r="J232" s="2">
-        <v>697.0</v>
+        <v>698.0</v>
       </c>
       <c r="K232" s="2">
         <v>1.0</v>
@@ -16798,13 +16798,13 @@
         <v>0.0</v>
       </c>
       <c r="N232" s="2">
-        <v>697.0</v>
+        <v>698.0</v>
       </c>
       <c r="O232" s="2">
         <v>20.0</v>
       </c>
       <c r="P232" s="2">
-        <v>128.0</v>
+        <v>129.0</v>
       </c>
       <c r="Q232" s="2">
         <v>549.0</v>
@@ -16857,7 +16857,7 @@
         <v>666.0</v>
       </c>
       <c r="J233" s="2">
-        <v>463.0</v>
+        <v>464.0</v>
       </c>
       <c r="K233" s="2">
         <v>1.0</v>
@@ -16869,10 +16869,10 @@
         <v>0.0</v>
       </c>
       <c r="N233" s="2">
-        <v>463.0</v>
+        <v>464.0</v>
       </c>
       <c r="O233" s="2">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="P233" s="2">
         <v>229.0</v>
